--- a/docs/Capacity alocation - pana in Dec 2026.xlsx
+++ b/docs/Capacity alocation - pana in Dec 2026.xlsx
@@ -1,48 +1,44 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr codeName="ThisWorkbook"/>
+  <bookViews>
+    <workbookView activeTab="1" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Alocări" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="Pe persoană" sheetId="2" r:id="rId5"/>
+    <sheet name="Alocări" sheetId="1" r:id="rId4"/>
+    <sheet name="Pe persoană" sheetId="2" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'Alocări'!$A$1:$M$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alocări'!$A$1:$M$66</definedName>
   </definedNames>
-  <calcPr/>
-  <extLst>
-    <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="RPWbH39Bw0iNHLX4qGdWnh5s6lFrr2Yx9yDTyeWskvM="/>
-    </ext>
-  </extLst>
+  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author/>
   </authors>
   <commentList>
-    <comment authorId="0" ref="G51">
+    <comment ref="G51" authorId="0">
       <text>
-        <t xml:space="preserve">======
+        <r>
+          <t xml:space="preserve">======
 ID#AAAB_HNPdjA
 Microsoft Office User    (2026-07-03 13:06:27)
 Posibil nevoie de externalizare</t>
+        </r>
       </text>
     </comment>
   </commentList>
-  <extLst>
-    <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId1" roundtripDataSignature="AMtx7miV1luEqmxkDX16p24IMuu0ZbhoVw=="/>
-    </ext>
-  </extLst>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="60">
   <si>
     <t>Client</t>
   </si>
@@ -227,48 +223,57 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.0;\(#,##0.0\);\-"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="5">
     <font>
-      <sz val="11.0"/>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11.0"/>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b/>
-      <sz val="11.0"/>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="4">
@@ -276,7 +281,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -291,61 +296,64 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
-    <border/>
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color rgb="FFD9D9D9"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="16">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center"/>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="2" numFmtId="164" fillId="0" borderId="1" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center"/>
+    <xf xfId="0" fontId="2" numFmtId="164" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center"/>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="2" numFmtId="164" fillId="3" borderId="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf borderId="2" fillId="3" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="2" fillId="3" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center"/>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="2" numFmtId="164" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="2" numFmtId="164" fillId="0" borderId="1" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="4" numFmtId="164" fillId="0" borderId="1" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="164" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="2" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="2" fillId="0" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center"/>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf xfId="0" fontId="3" numFmtId="165" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
 </styleSheet>
 </file>
 
@@ -358,14 +366,14 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
@@ -419,159 +427,207 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr filterMode="1">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <dimension ref="A1:Z1002"/>
+  <sheetFormatPr customHeight="true" defaultRowHeight="15" defaultColWidth="14.43" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="24.43"/>
-    <col customWidth="1" min="2" max="2" width="26.0"/>
-    <col customWidth="1" min="3" max="3" width="20.0"/>
-    <col customWidth="1" min="4" max="4" width="12.0"/>
-    <col customWidth="1" min="5" max="5" width="12.43"/>
-    <col customWidth="1" min="6" max="6" width="16.0"/>
-    <col customWidth="1" min="7" max="7" width="14.86"/>
-    <col customWidth="1" min="8" max="8" width="17.71"/>
-    <col customWidth="1" min="9" max="12" width="18.71"/>
-    <col customWidth="1" min="13" max="13" width="11.0"/>
-    <col customWidth="1" min="14" max="26" width="8.71"/>
+    <col min="1" max="1" width="24.43" customWidth="true" style="0"/>
+    <col min="2" max="2" width="26" customWidth="true" style="0"/>
+    <col min="3" max="3" width="20" customWidth="true" style="0"/>
+    <col min="4" max="4" width="12" customWidth="true" style="0"/>
+    <col min="5" max="5" width="12.43" customWidth="true" style="0"/>
+    <col min="6" max="6" width="16" customWidth="true" style="0"/>
+    <col min="7" max="7" width="14.86" customWidth="true" style="0"/>
+    <col min="8" max="8" width="17.71" customWidth="true" style="0"/>
+    <col min="9" max="9" width="18.71" customWidth="true" style="0"/>
+    <col min="10" max="10" width="18.71" customWidth="true" style="0"/>
+    <col min="11" max="11" width="18.71" customWidth="true" style="0"/>
+    <col min="12" max="12" width="18.71" customWidth="true" style="0"/>
+    <col min="13" max="13" width="11" customWidth="true" style="0"/>
+    <col min="14" max="14" width="8.71" customWidth="true" style="0"/>
+    <col min="15" max="15" width="8.71" customWidth="true" style="0"/>
+    <col min="16" max="16" width="8.71" customWidth="true" style="0"/>
+    <col min="17" max="17" width="8.71" customWidth="true" style="0"/>
+    <col min="18" max="18" width="8.71" customWidth="true" style="0"/>
+    <col min="19" max="19" width="8.71" customWidth="true" style="0"/>
+    <col min="20" max="20" width="8.71" customWidth="true" style="0"/>
+    <col min="21" max="21" width="8.71" customWidth="true" style="0"/>
+    <col min="22" max="22" width="8.71" customWidth="true" style="0"/>
+    <col min="23" max="23" width="8.71" customWidth="true" style="0"/>
+    <col min="24" max="24" width="8.71" customWidth="true" style="0"/>
+    <col min="25" max="25" width="8.71" customWidth="true" style="0"/>
+    <col min="26" max="26" width="8.71" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:26">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -610,7 +666,7 @@
       </c>
       <c r="M1" s="1"/>
     </row>
-    <row r="2">
+    <row r="2" spans="1:26">
       <c r="A2" s="2" t="s">
         <v>12</v>
       </c>
@@ -648,11 +704,11 @@
         <v>3.0</v>
       </c>
       <c r="M2" s="3">
-        <f t="shared" ref="M2:M5" si="1">SUM(E2:L2)</f>
+        <f>SUM(E2:L2)</f>
         <v>18</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:26">
       <c r="A3" s="2" t="s">
         <v>16</v>
       </c>
@@ -690,11 +746,11 @@
         <v>20.0</v>
       </c>
       <c r="M3" s="3">
-        <f t="shared" si="1"/>
+        <f>SUM(E3:L3)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:26">
       <c r="A4" s="2" t="s">
         <v>16</v>
       </c>
@@ -732,11 +788,11 @@
         <v>20.0</v>
       </c>
       <c r="M4" s="3">
-        <f t="shared" si="1"/>
+        <f>SUM(E4:L4)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:26">
       <c r="A5" s="2" t="s">
         <v>16</v>
       </c>
@@ -774,11 +830,11 @@
         <v>60.0</v>
       </c>
       <c r="M5" s="3">
-        <f t="shared" si="1"/>
+        <f>SUM(E5:L5)</f>
         <v>300</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:26">
       <c r="A6" s="2" t="s">
         <v>16</v>
       </c>
@@ -817,7 +873,7 @@
       </c>
       <c r="M6" s="3"/>
     </row>
-    <row r="7">
+    <row r="7" spans="1:26">
       <c r="A7" s="2" t="s">
         <v>16</v>
       </c>
@@ -855,11 +911,11 @@
         <v>40.0</v>
       </c>
       <c r="M7" s="3">
-        <f t="shared" ref="M7:M42" si="2">SUM(E7:L7)</f>
+        <f>SUM(E7:L7)</f>
         <v>240</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:26">
       <c r="A8" s="2" t="s">
         <v>24</v>
       </c>
@@ -897,11 +953,11 @@
         <v>3.0</v>
       </c>
       <c r="M8" s="3">
-        <f t="shared" si="2"/>
+        <f>SUM(E8:L8)</f>
         <v>18</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:26">
       <c r="A9" s="2" t="s">
         <v>24</v>
       </c>
@@ -939,11 +995,11 @@
         <v>3.0</v>
       </c>
       <c r="M9" s="3">
-        <f t="shared" si="2"/>
+        <f>SUM(E9:L9)</f>
         <v>18</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:26">
       <c r="A10" s="2" t="s">
         <v>25</v>
       </c>
@@ -981,11 +1037,11 @@
         <v>20.7</v>
       </c>
       <c r="M10" s="3">
-        <f t="shared" si="2"/>
-        <v>165.6</v>
-      </c>
-    </row>
-    <row r="11">
+        <f>SUM(E10:L10)</f>
+        <v>165.59999999999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26">
       <c r="A11" s="2" t="s">
         <v>25</v>
       </c>
@@ -1023,11 +1079,11 @@
         <v>20.7</v>
       </c>
       <c r="M11" s="3">
-        <f t="shared" si="2"/>
-        <v>165.6</v>
-      </c>
-    </row>
-    <row r="12">
+        <f>SUM(E11:L11)</f>
+        <v>165.59999999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26">
       <c r="A12" s="2" t="s">
         <v>25</v>
       </c>
@@ -1065,11 +1121,11 @@
         <v>13.8</v>
       </c>
       <c r="M12" s="3">
-        <f t="shared" si="2"/>
-        <v>110.4</v>
-      </c>
-    </row>
-    <row r="13">
+        <f>SUM(E12:L12)</f>
+        <v>110.39999999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26">
       <c r="A13" s="2" t="s">
         <v>25</v>
       </c>
@@ -1092,31 +1148,31 @@
         <v>13.8</v>
       </c>
       <c r="H13" s="3">
-        <f t="shared" ref="H13:L13" si="3">13.8+20.7</f>
+        <f>13.8+20.7</f>
         <v>34.5</v>
       </c>
       <c r="I13" s="3">
-        <f t="shared" si="3"/>
+        <f>13.8+20.7</f>
         <v>34.5</v>
       </c>
       <c r="J13" s="3">
-        <f t="shared" si="3"/>
+        <f>13.8+20.7</f>
         <v>34.5</v>
       </c>
       <c r="K13" s="3">
-        <f t="shared" si="3"/>
+        <f>13.8+20.7</f>
         <v>34.5</v>
       </c>
       <c r="L13" s="3">
-        <f t="shared" si="3"/>
+        <f>13.8+20.7</f>
         <v>34.5</v>
       </c>
       <c r="M13" s="3">
-        <f t="shared" si="2"/>
-        <v>213.9</v>
-      </c>
-    </row>
-    <row r="14">
+        <f>SUM(E13:L13)</f>
+        <v>213.90000000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26">
       <c r="A14" s="2" t="s">
         <v>25</v>
       </c>
@@ -1144,11 +1200,11 @@
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3">
-        <f t="shared" si="2"/>
-        <v>62.1</v>
-      </c>
-    </row>
-    <row r="15">
+        <f>SUM(E14:L14)</f>
+        <v>62.099999999999994</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26">
       <c r="A15" s="2" t="s">
         <v>25</v>
       </c>
@@ -1186,11 +1242,11 @@
         <v>20.7</v>
       </c>
       <c r="M15" s="3">
-        <f t="shared" si="2"/>
-        <v>269.1</v>
-      </c>
-    </row>
-    <row r="16">
+        <f>SUM(E15:L15)</f>
+        <v>269.099999999999966</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26">
       <c r="A16" s="2" t="s">
         <v>25</v>
       </c>
@@ -1224,11 +1280,11 @@
         <v>20.0</v>
       </c>
       <c r="M16" s="3">
-        <f t="shared" si="2"/>
+        <f>SUM(E16:L16)</f>
         <v>120</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:26">
       <c r="A17" s="2" t="s">
         <v>25</v>
       </c>
@@ -1262,11 +1318,11 @@
         <v>50.0</v>
       </c>
       <c r="M17" s="3">
-        <f t="shared" si="2"/>
+        <f>SUM(E17:L17)</f>
         <v>300</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:26">
       <c r="A18" s="2" t="s">
         <v>25</v>
       </c>
@@ -1300,11 +1356,11 @@
         <v>50.0</v>
       </c>
       <c r="M18" s="3">
-        <f t="shared" si="2"/>
+        <f>SUM(E18:L18)</f>
         <v>300</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:26">
       <c r="A19" s="2" t="s">
         <v>31</v>
       </c>
@@ -1342,11 +1398,11 @@
         <v>8.0</v>
       </c>
       <c r="M19" s="3">
-        <f t="shared" si="2"/>
+        <f>SUM(E19:L19)</f>
         <v>240</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:26">
       <c r="A20" s="2" t="s">
         <v>31</v>
       </c>
@@ -1384,11 +1440,11 @@
         <v>8.0</v>
       </c>
       <c r="M20" s="3">
-        <f t="shared" si="2"/>
+        <f>SUM(E20:L20)</f>
         <v>40</v>
       </c>
     </row>
-    <row r="21" ht="15.75" customHeight="1">
+    <row r="21" spans="1:26" customHeight="1" ht="15.75">
       <c r="A21" s="2" t="s">
         <v>31</v>
       </c>
@@ -1426,11 +1482,11 @@
         <v>56.0</v>
       </c>
       <c r="M21" s="3">
-        <f t="shared" si="2"/>
+        <f>SUM(E21:L21)</f>
         <v>396.5</v>
       </c>
     </row>
-    <row r="22" ht="15.75" customHeight="1">
+    <row r="22" spans="1:26" customHeight="1" ht="15.75">
       <c r="A22" s="2" t="s">
         <v>36</v>
       </c>
@@ -1468,11 +1524,11 @@
         <v>8.0</v>
       </c>
       <c r="M22" s="3">
-        <f t="shared" si="2"/>
+        <f>SUM(E22:L22)</f>
         <v>65.2</v>
       </c>
     </row>
-    <row r="23" ht="15.75" customHeight="1">
+    <row r="23" spans="1:26" customHeight="1" ht="15.75">
       <c r="A23" s="2" t="s">
         <v>36</v>
       </c>
@@ -1510,11 +1566,11 @@
         <v>0.0</v>
       </c>
       <c r="M23" s="3">
-        <f t="shared" si="2"/>
+        <f>SUM(E23:L23)</f>
         <v>29</v>
       </c>
     </row>
-    <row r="24" ht="15.75" customHeight="1">
+    <row r="24" spans="1:26" customHeight="1" ht="15.75">
       <c r="A24" s="2" t="s">
         <v>36</v>
       </c>
@@ -1552,11 +1608,11 @@
         <v>0.0</v>
       </c>
       <c r="M24" s="3">
-        <f t="shared" si="2"/>
+        <f>SUM(E24:L24)</f>
         <v>48.3</v>
       </c>
     </row>
-    <row r="25" ht="15.75" customHeight="1">
+    <row r="25" spans="1:26" customHeight="1" ht="15.75">
       <c r="A25" s="2" t="s">
         <v>36</v>
       </c>
@@ -1594,11 +1650,11 @@
         <v>5.0</v>
       </c>
       <c r="M25" s="3">
-        <f t="shared" si="2"/>
+        <f>SUM(E25:L25)</f>
         <v>133.5</v>
       </c>
     </row>
-    <row r="26" ht="15.75" customHeight="1">
+    <row r="26" spans="1:26" customHeight="1" ht="15.75">
       <c r="A26" s="2" t="s">
         <v>36</v>
       </c>
@@ -1636,11 +1692,11 @@
         <v>0.0</v>
       </c>
       <c r="M26" s="3">
-        <f t="shared" si="2"/>
+        <f>SUM(E26:L26)</f>
         <v>64.3</v>
       </c>
     </row>
-    <row r="27" ht="15.75" customHeight="1">
+    <row r="27" spans="1:26" customHeight="1" ht="15.75">
       <c r="A27" s="2" t="s">
         <v>36</v>
       </c>
@@ -1678,11 +1734,11 @@
         <v>8.0</v>
       </c>
       <c r="M27" s="3">
-        <f t="shared" si="2"/>
-        <v>137.1</v>
-      </c>
-    </row>
-    <row r="28" ht="15.75" customHeight="1">
+        <f>SUM(E27:L27)</f>
+        <v>137.099999999999994</v>
+      </c>
+    </row>
+    <row r="28" spans="1:26" customHeight="1" ht="15.75">
       <c r="A28" s="2" t="s">
         <v>36</v>
       </c>
@@ -1720,11 +1776,11 @@
         <v>4.0</v>
       </c>
       <c r="M28" s="3">
-        <f t="shared" si="2"/>
-        <v>91.6</v>
-      </c>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
+        <f>SUM(E28:L28)</f>
+        <v>91.59999999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:26" customHeight="1" ht="15.75">
       <c r="A29" s="2" t="s">
         <v>36</v>
       </c>
@@ -1752,11 +1808,11 @@
       <c r="K29" s="3"/>
       <c r="L29" s="3"/>
       <c r="M29" s="3">
-        <f t="shared" si="2"/>
+        <f>SUM(E29:L29)</f>
         <v>30</v>
       </c>
     </row>
-    <row r="30" ht="15.75" customHeight="1">
+    <row r="30" spans="1:26" customHeight="1" ht="15.75">
       <c r="A30" s="2" t="s">
         <v>36</v>
       </c>
@@ -1784,11 +1840,11 @@
       <c r="K30" s="3"/>
       <c r="L30" s="3"/>
       <c r="M30" s="3">
-        <f t="shared" si="2"/>
+        <f>SUM(E30:L30)</f>
         <v>60</v>
       </c>
     </row>
-    <row r="31" ht="15.75" customHeight="1">
+    <row r="31" spans="1:26" customHeight="1" ht="15.75">
       <c r="A31" s="2" t="s">
         <v>36</v>
       </c>
@@ -1816,11 +1872,11 @@
       <c r="K31" s="3"/>
       <c r="L31" s="3"/>
       <c r="M31" s="3">
-        <f t="shared" si="2"/>
+        <f>SUM(E31:L31)</f>
         <v>241</v>
       </c>
     </row>
-    <row r="32" ht="15.75" customHeight="1">
+    <row r="32" spans="1:26" customHeight="1" ht="15.75">
       <c r="A32" s="2" t="s">
         <v>36</v>
       </c>
@@ -1854,11 +1910,11 @@
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
       <c r="M32" s="3">
-        <f t="shared" si="2"/>
-        <v>170.8</v>
-      </c>
-    </row>
-    <row r="33" ht="15.75" customHeight="1">
+        <f>SUM(E32:L32)</f>
+        <v>170.80000000000001</v>
+      </c>
+    </row>
+    <row r="33" spans="1:26" customHeight="1" ht="15.75">
       <c r="A33" s="2" t="s">
         <v>36</v>
       </c>
@@ -1886,11 +1942,11 @@
       <c r="K33" s="3"/>
       <c r="L33" s="3"/>
       <c r="M33" s="3">
-        <f t="shared" si="2"/>
+        <f>SUM(E33:L33)</f>
         <v>18</v>
       </c>
     </row>
-    <row r="34" ht="15.75" customHeight="1">
+    <row r="34" spans="1:26" customHeight="1" ht="15.75">
       <c r="A34" s="2" t="s">
         <v>36</v>
       </c>
@@ -1916,11 +1972,11 @@
       <c r="K34" s="3"/>
       <c r="L34" s="3"/>
       <c r="M34" s="3">
-        <f t="shared" si="2"/>
+        <f>SUM(E34:L34)</f>
         <v>48.3</v>
       </c>
     </row>
-    <row r="35" ht="15.75" customHeight="1">
+    <row r="35" spans="1:26" customHeight="1" ht="15.75">
       <c r="A35" s="2" t="s">
         <v>43</v>
       </c>
@@ -1958,11 +2014,11 @@
         <v>8.0</v>
       </c>
       <c r="M35" s="3">
-        <f t="shared" si="2"/>
+        <f>SUM(E35:L35)</f>
         <v>56.8</v>
       </c>
     </row>
-    <row r="36" ht="15.75" customHeight="1">
+    <row r="36" spans="1:26" customHeight="1" ht="15.75">
       <c r="A36" s="2" t="s">
         <v>47</v>
       </c>
@@ -2000,11 +2056,11 @@
         <v>0.0</v>
       </c>
       <c r="M36" s="3">
-        <f t="shared" si="2"/>
+        <f>SUM(E36:L36)</f>
         <v>26.2</v>
       </c>
     </row>
-    <row r="37" ht="15.75" customHeight="1">
+    <row r="37" spans="1:26" customHeight="1" ht="15.75">
       <c r="A37" s="2" t="s">
         <v>47</v>
       </c>
@@ -2021,7 +2077,7 @@
         <v>95.2</v>
       </c>
       <c r="F37" s="3">
-        <v>75.9</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="G37" s="3">
         <v>100.0</v>
@@ -2042,11 +2098,11 @@
         <v>100.0</v>
       </c>
       <c r="M37" s="3">
-        <f t="shared" si="2"/>
-        <v>771.1</v>
-      </c>
-    </row>
-    <row r="38" ht="15.75" customHeight="1">
+        <f>SUM(E37:L37)</f>
+        <v>771.10000000000002</v>
+      </c>
+    </row>
+    <row r="38" spans="1:26" customHeight="1" ht="15.75">
       <c r="A38" s="2" t="s">
         <v>47</v>
       </c>
@@ -2084,11 +2140,11 @@
         <v>0.0</v>
       </c>
       <c r="M38" s="3">
-        <f t="shared" si="2"/>
-        <v>70.4</v>
-      </c>
-    </row>
-    <row r="39" ht="15.75" customHeight="1">
+        <f>SUM(E38:L38)</f>
+        <v>70.40000000000001</v>
+      </c>
+    </row>
+    <row r="39" spans="1:26" customHeight="1" ht="15.75">
       <c r="A39" s="2" t="s">
         <v>47</v>
       </c>
@@ -2126,11 +2182,11 @@
         <v>0.0</v>
       </c>
       <c r="M39" s="3">
-        <f t="shared" si="2"/>
-        <v>72.4</v>
-      </c>
-    </row>
-    <row r="40" ht="15.75" customHeight="1">
+        <f>SUM(E39:L39)</f>
+        <v>72.40000000000001</v>
+      </c>
+    </row>
+    <row r="40" spans="1:26" customHeight="1" ht="15.75">
       <c r="A40" s="2" t="s">
         <v>47</v>
       </c>
@@ -2168,11 +2224,11 @@
         <v>0.0</v>
       </c>
       <c r="M40" s="3">
-        <f t="shared" si="2"/>
-        <v>96.6</v>
-      </c>
-    </row>
-    <row r="41" ht="15.75" customHeight="1">
+        <f>SUM(E40:L40)</f>
+        <v>96.59999999999999</v>
+      </c>
+    </row>
+    <row r="41" spans="1:26" customHeight="1" ht="15.75">
       <c r="A41" s="2" t="s">
         <v>47</v>
       </c>
@@ -2210,11 +2266,11 @@
         <v>0.0</v>
       </c>
       <c r="M41" s="3">
-        <f t="shared" si="2"/>
+        <f>SUM(E41:L41)</f>
         <v>69</v>
       </c>
     </row>
-    <row r="42" ht="15.75" customHeight="1">
+    <row r="42" spans="1:26" customHeight="1" ht="15.75">
       <c r="A42" s="2" t="s">
         <v>47</v>
       </c>
@@ -2252,11 +2308,11 @@
         <v>80.0</v>
       </c>
       <c r="M42" s="3">
-        <f t="shared" si="2"/>
+        <f>SUM(E42:L42)</f>
         <v>549</v>
       </c>
     </row>
-    <row r="43" ht="15.75" customHeight="1">
+    <row r="43" spans="1:26" customHeight="1" ht="15.75">
       <c r="A43" s="2" t="s">
         <v>47</v>
       </c>
@@ -2283,7 +2339,7 @@
       <c r="L43" s="3"/>
       <c r="M43" s="3"/>
     </row>
-    <row r="44" ht="15.75" customHeight="1">
+    <row r="44" spans="1:26" customHeight="1" ht="15.75">
       <c r="A44" s="2" t="s">
         <v>51</v>
       </c>
@@ -2317,11 +2373,11 @@
         <v>0.0</v>
       </c>
       <c r="M44" s="3">
-        <f t="shared" ref="M44:M46" si="4">SUM(E44:L44)</f>
-        <v>37.9</v>
-      </c>
-    </row>
-    <row r="45" ht="15.75" customHeight="1">
+        <f>SUM(E44:L44)</f>
+        <v>37.90000000000001</v>
+      </c>
+    </row>
+    <row r="45" spans="1:26" customHeight="1" ht="15.75">
       <c r="A45" s="2" t="s">
         <v>51</v>
       </c>
@@ -2355,11 +2411,11 @@
         <v>0.0</v>
       </c>
       <c r="M45" s="3">
-        <f t="shared" si="4"/>
+        <f>SUM(E45:L45)</f>
         <v>26.6</v>
       </c>
     </row>
-    <row r="46" ht="15.75" customHeight="1">
+    <row r="46" spans="1:26" customHeight="1" ht="15.75">
       <c r="A46" s="2" t="s">
         <v>51</v>
       </c>
@@ -2397,11 +2453,11 @@
         <v>2.0</v>
       </c>
       <c r="M46" s="3">
-        <f t="shared" si="4"/>
-        <v>228.7</v>
-      </c>
-    </row>
-    <row r="47" ht="15.75" customHeight="1">
+        <f>SUM(E46:L46)</f>
+        <v>228.69999999999999</v>
+      </c>
+    </row>
+    <row r="47" spans="1:26" customHeight="1" ht="15.75">
       <c r="A47" s="2" t="s">
         <v>51</v>
       </c>
@@ -2440,7 +2496,7 @@
       </c>
       <c r="M47" s="3"/>
     </row>
-    <row r="48" ht="15.75" customHeight="1">
+    <row r="48" spans="1:26" customHeight="1" ht="15.75">
       <c r="A48" s="2" t="s">
         <v>51</v>
       </c>
@@ -2474,11 +2530,11 @@
         <v>2.0</v>
       </c>
       <c r="M48" s="3">
-        <f t="shared" ref="M48:M51" si="5">SUM(E48:L48)</f>
+        <f>SUM(E48:L48)</f>
         <v>12</v>
       </c>
     </row>
-    <row r="49" ht="15.75" customHeight="1">
+    <row r="49" spans="1:26" customHeight="1" ht="15.75">
       <c r="A49" s="2" t="s">
         <v>52</v>
       </c>
@@ -2516,11 +2572,11 @@
         <v>0.0</v>
       </c>
       <c r="M49" s="3">
-        <f t="shared" si="5"/>
-        <v>106.1</v>
-      </c>
-    </row>
-    <row r="50" ht="15.75" customHeight="1">
+        <f>SUM(E49:L49)</f>
+        <v>106.10000000000001</v>
+      </c>
+    </row>
+    <row r="50" spans="1:26" customHeight="1" ht="15.75">
       <c r="A50" s="2" t="s">
         <v>52</v>
       </c>
@@ -2558,11 +2614,11 @@
         <v>0.0</v>
       </c>
       <c r="M50" s="3">
-        <f t="shared" si="5"/>
+        <f>SUM(E50:L50)</f>
         <v>53</v>
       </c>
     </row>
-    <row r="51" ht="15.75" customHeight="1">
+    <row r="51" spans="1:26" customHeight="1" ht="15.75">
       <c r="A51" s="2" t="s">
         <v>52</v>
       </c>
@@ -2584,11 +2640,11 @@
       <c r="K51" s="3"/>
       <c r="L51" s="3"/>
       <c r="M51" s="3">
-        <f t="shared" si="5"/>
+        <f>SUM(E51:L51)</f>
         <v>40</v>
       </c>
     </row>
-    <row r="52" ht="15.75" customHeight="1">
+    <row r="52" spans="1:26" customHeight="1" ht="15.75">
       <c r="A52" s="2" t="s">
         <v>52</v>
       </c>
@@ -2627,7 +2683,7 @@
       </c>
       <c r="M52" s="3"/>
     </row>
-    <row r="53" ht="15.75" customHeight="1">
+    <row r="53" spans="1:26" customHeight="1" ht="15.75">
       <c r="A53" s="2" t="s">
         <v>53</v>
       </c>
@@ -2665,11 +2721,11 @@
         <v>0.0</v>
       </c>
       <c r="M53" s="3">
-        <f t="shared" ref="M53:M55" si="6">SUM(E53:L53)</f>
+        <f>SUM(E53:L53)</f>
         <v>82.8</v>
       </c>
     </row>
-    <row r="54" ht="15.75" customHeight="1">
+    <row r="54" spans="1:26" customHeight="1" ht="15.75">
       <c r="A54" s="2" t="s">
         <v>53</v>
       </c>
@@ -2707,11 +2763,11 @@
         <v>0.0</v>
       </c>
       <c r="M54" s="3">
-        <f t="shared" si="6"/>
+        <f>SUM(E54:L54)</f>
         <v>69</v>
       </c>
     </row>
-    <row r="55" ht="15.75" customHeight="1">
+    <row r="55" spans="1:26" customHeight="1" ht="15.75">
       <c r="A55" s="2" t="s">
         <v>53</v>
       </c>
@@ -2741,11 +2797,11 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3">
-        <f t="shared" si="6"/>
+        <f>SUM(E55:L55)</f>
         <v>184</v>
       </c>
     </row>
-    <row r="56" ht="15.75" customHeight="1">
+    <row r="56" spans="1:26" customHeight="1" ht="15.75">
       <c r="A56" s="6" t="s">
         <v>52</v>
       </c>
@@ -2793,7 +2849,7 @@
       <c r="Y56" s="8"/>
       <c r="Z56" s="8"/>
     </row>
-    <row r="57" ht="15.75" customHeight="1">
+    <row r="57" spans="1:26" customHeight="1" ht="15.75">
       <c r="A57" s="6" t="s">
         <v>53</v>
       </c>
@@ -2841,7 +2897,7 @@
       <c r="Y57" s="8"/>
       <c r="Z57" s="8"/>
     </row>
-    <row r="58" ht="15.75" customHeight="1">
+    <row r="58" spans="1:26" customHeight="1" ht="15.75">
       <c r="A58" s="2" t="s">
         <v>53</v>
       </c>
@@ -2880,7 +2936,7 @@
       </c>
       <c r="M58" s="3"/>
     </row>
-    <row r="59" ht="15.75" customHeight="1">
+    <row r="59" spans="1:26" customHeight="1" ht="15.75">
       <c r="A59" s="2" t="s">
         <v>56</v>
       </c>
@@ -2916,11 +2972,11 @@
         <v>0.0</v>
       </c>
       <c r="M59" s="3">
-        <f t="shared" ref="M59:M61" si="7">SUM(E59:L59)</f>
+        <f>SUM(E59:L59)</f>
         <v>207</v>
       </c>
     </row>
-    <row r="60" ht="15.75" customHeight="1">
+    <row r="60" spans="1:26" customHeight="1" ht="15.75">
       <c r="A60" s="2" t="s">
         <v>56</v>
       </c>
@@ -2958,11 +3014,11 @@
         <v>0.0</v>
       </c>
       <c r="M60" s="3">
-        <f t="shared" si="7"/>
+        <f>SUM(E60:L60)</f>
         <v>480</v>
       </c>
     </row>
-    <row r="61" ht="15.75" customHeight="1">
+    <row r="61" spans="1:26" customHeight="1" ht="15.75">
       <c r="A61" s="2" t="s">
         <v>56</v>
       </c>
@@ -3000,11 +3056,11 @@
         <v>0.0</v>
       </c>
       <c r="M61" s="3">
-        <f t="shared" si="7"/>
+        <f>SUM(E61:L61)</f>
         <v>372.5</v>
       </c>
     </row>
-    <row r="62" ht="15.75" customHeight="1">
+    <row r="62" spans="1:26" customHeight="1" ht="15.75">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
@@ -3019,7 +3075,7 @@
       <c r="L62" s="5"/>
       <c r="M62" s="3"/>
     </row>
-    <row r="63" ht="15.75" customHeight="1">
+    <row r="63" spans="1:26" customHeight="1" ht="15.75">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
@@ -3032,7 +3088,7 @@
       <c r="L63" s="9"/>
       <c r="M63" s="10"/>
     </row>
-    <row r="64" ht="15.75" customHeight="1">
+    <row r="64" spans="1:26" customHeight="1" ht="15.75">
       <c r="A64" s="11" t="s">
         <v>58</v>
       </c>
@@ -3040,43 +3096,43 @@
       <c r="C64" s="11"/>
       <c r="D64" s="11"/>
       <c r="E64" s="12">
-        <f t="shared" ref="E64:M64" si="8">SUM(E2:E61)</f>
-        <v>1429.7</v>
+        <f>SUM(E2:E61)</f>
+        <v>1429.70000000000027</v>
       </c>
       <c r="F64" s="12">
-        <f t="shared" si="8"/>
-        <v>1469.8</v>
+        <f>SUM(F2:F61)</f>
+        <v>1469.80000000000018</v>
       </c>
       <c r="G64" s="12">
-        <f t="shared" si="8"/>
-        <v>1440.4</v>
+        <f>SUM(G2:G61)</f>
+        <v>1440.40000000000009</v>
       </c>
       <c r="H64" s="12">
-        <f t="shared" si="8"/>
-        <v>1104.1</v>
+        <f>SUM(H2:H61)</f>
+        <v>1104.099999999999909</v>
       </c>
       <c r="I64" s="12">
-        <f t="shared" si="8"/>
-        <v>846.4</v>
+        <f>SUM(I2:I61)</f>
+        <v>846.39999999999998</v>
       </c>
       <c r="J64" s="12">
-        <f t="shared" si="8"/>
-        <v>741.4</v>
+        <f>SUM(J2:J61)</f>
+        <v>741.39999999999998</v>
       </c>
       <c r="K64" s="12">
-        <f t="shared" si="8"/>
-        <v>684.4</v>
+        <f>SUM(K2:K61)</f>
+        <v>684.39999999999998</v>
       </c>
       <c r="L64" s="12">
-        <f t="shared" si="8"/>
-        <v>712.4</v>
+        <f>SUM(L2:L61)</f>
+        <v>712.39999999999998</v>
       </c>
       <c r="M64" s="12">
-        <f t="shared" si="8"/>
-        <v>7925.4</v>
-      </c>
-    </row>
-    <row r="65" ht="15.75" customHeight="1">
+        <f>SUM(M2:M61)</f>
+        <v>7925.40000000000055</v>
+      </c>
+    </row>
+    <row r="65" spans="1:26" customHeight="1" ht="15.75">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
@@ -3091,971 +3147,990 @@
       <c r="L65" s="5"/>
       <c r="M65" s="4"/>
     </row>
-    <row r="66" ht="15.75" customHeight="1"/>
-    <row r="67" ht="15.75" customHeight="1"/>
-    <row r="68" ht="15.75" customHeight="1"/>
-    <row r="69" ht="15.75" customHeight="1"/>
-    <row r="70" ht="15.75" customHeight="1"/>
-    <row r="71" ht="15.75" customHeight="1"/>
-    <row r="72" ht="15.75" customHeight="1"/>
-    <row r="73" ht="15.75" customHeight="1"/>
-    <row r="74" ht="15.75" customHeight="1"/>
-    <row r="75" ht="15.75" customHeight="1"/>
-    <row r="76" ht="15.75" customHeight="1"/>
-    <row r="77" ht="15.75" customHeight="1"/>
-    <row r="78" ht="15.75" customHeight="1"/>
-    <row r="79" ht="15.75" customHeight="1"/>
-    <row r="80" ht="15.75" customHeight="1"/>
-    <row r="81" ht="15.75" customHeight="1"/>
-    <row r="82" ht="15.75" customHeight="1"/>
-    <row r="83" ht="15.75" customHeight="1"/>
-    <row r="84" ht="15.75" customHeight="1"/>
-    <row r="85" ht="15.75" customHeight="1"/>
-    <row r="86" ht="15.75" customHeight="1"/>
-    <row r="87" ht="15.75" customHeight="1"/>
-    <row r="88" ht="15.75" customHeight="1"/>
-    <row r="89" ht="15.75" customHeight="1"/>
-    <row r="90" ht="15.75" customHeight="1"/>
-    <row r="91" ht="15.75" customHeight="1"/>
-    <row r="92" ht="15.75" customHeight="1"/>
-    <row r="93" ht="15.75" customHeight="1"/>
-    <row r="94" ht="15.75" customHeight="1"/>
-    <row r="95" ht="15.75" customHeight="1"/>
-    <row r="96" ht="15.75" customHeight="1"/>
-    <row r="97" ht="15.75" customHeight="1"/>
-    <row r="98" ht="15.75" customHeight="1"/>
-    <row r="99" ht="15.75" customHeight="1"/>
-    <row r="100" ht="15.75" customHeight="1"/>
-    <row r="101" ht="15.75" customHeight="1"/>
-    <row r="102" ht="15.75" customHeight="1"/>
-    <row r="103" ht="15.75" customHeight="1"/>
-    <row r="104" ht="15.75" customHeight="1"/>
-    <row r="105" ht="15.75" customHeight="1"/>
-    <row r="106" ht="15.75" customHeight="1"/>
-    <row r="107" ht="15.75" customHeight="1"/>
-    <row r="108" ht="15.75" customHeight="1"/>
-    <row r="109" ht="15.75" customHeight="1"/>
-    <row r="110" ht="15.75" customHeight="1"/>
-    <row r="111" ht="15.75" customHeight="1"/>
-    <row r="112" ht="15.75" customHeight="1"/>
-    <row r="113" ht="15.75" customHeight="1"/>
-    <row r="114" ht="15.75" customHeight="1"/>
-    <row r="115" ht="15.75" customHeight="1"/>
-    <row r="116" ht="15.75" customHeight="1"/>
-    <row r="117" ht="15.75" customHeight="1"/>
-    <row r="118" ht="15.75" customHeight="1"/>
-    <row r="119" ht="15.75" customHeight="1"/>
-    <row r="120" ht="15.75" customHeight="1"/>
-    <row r="121" ht="15.75" customHeight="1"/>
-    <row r="122" ht="15.75" customHeight="1"/>
-    <row r="123" ht="15.75" customHeight="1"/>
-    <row r="124" ht="15.75" customHeight="1"/>
-    <row r="125" ht="15.75" customHeight="1"/>
-    <row r="126" ht="15.75" customHeight="1"/>
-    <row r="127" ht="15.75" customHeight="1"/>
-    <row r="128" ht="15.75" customHeight="1"/>
-    <row r="129" ht="15.75" customHeight="1"/>
-    <row r="130" ht="15.75" customHeight="1"/>
-    <row r="131" ht="15.75" customHeight="1"/>
-    <row r="132" ht="15.75" customHeight="1"/>
-    <row r="133" ht="15.75" customHeight="1"/>
-    <row r="134" ht="15.75" customHeight="1"/>
-    <row r="135" ht="15.75" customHeight="1"/>
-    <row r="136" ht="15.75" customHeight="1"/>
-    <row r="137" ht="15.75" customHeight="1"/>
-    <row r="138" ht="15.75" customHeight="1"/>
-    <row r="139" ht="15.75" customHeight="1"/>
-    <row r="140" ht="15.75" customHeight="1"/>
-    <row r="141" ht="15.75" customHeight="1"/>
-    <row r="142" ht="15.75" customHeight="1"/>
-    <row r="143" ht="15.75" customHeight="1"/>
-    <row r="144" ht="15.75" customHeight="1"/>
-    <row r="145" ht="15.75" customHeight="1"/>
-    <row r="146" ht="15.75" customHeight="1"/>
-    <row r="147" ht="15.75" customHeight="1"/>
-    <row r="148" ht="15.75" customHeight="1"/>
-    <row r="149" ht="15.75" customHeight="1"/>
-    <row r="150" ht="15.75" customHeight="1"/>
-    <row r="151" ht="15.75" customHeight="1"/>
-    <row r="152" ht="15.75" customHeight="1"/>
-    <row r="153" ht="15.75" customHeight="1"/>
-    <row r="154" ht="15.75" customHeight="1"/>
-    <row r="155" ht="15.75" customHeight="1"/>
-    <row r="156" ht="15.75" customHeight="1"/>
-    <row r="157" ht="15.75" customHeight="1"/>
-    <row r="158" ht="15.75" customHeight="1"/>
-    <row r="159" ht="15.75" customHeight="1"/>
-    <row r="160" ht="15.75" customHeight="1"/>
-    <row r="161" ht="15.75" customHeight="1"/>
-    <row r="162" ht="15.75" customHeight="1"/>
-    <row r="163" ht="15.75" customHeight="1"/>
-    <row r="164" ht="15.75" customHeight="1"/>
-    <row r="165" ht="15.75" customHeight="1"/>
-    <row r="166" ht="15.75" customHeight="1"/>
-    <row r="167" ht="15.75" customHeight="1"/>
-    <row r="168" ht="15.75" customHeight="1"/>
-    <row r="169" ht="15.75" customHeight="1"/>
-    <row r="170" ht="15.75" customHeight="1"/>
-    <row r="171" ht="15.75" customHeight="1"/>
-    <row r="172" ht="15.75" customHeight="1"/>
-    <row r="173" ht="15.75" customHeight="1"/>
-    <row r="174" ht="15.75" customHeight="1"/>
-    <row r="175" ht="15.75" customHeight="1"/>
-    <row r="176" ht="15.75" customHeight="1"/>
-    <row r="177" ht="15.75" customHeight="1"/>
-    <row r="178" ht="15.75" customHeight="1"/>
-    <row r="179" ht="15.75" customHeight="1"/>
-    <row r="180" ht="15.75" customHeight="1"/>
-    <row r="181" ht="15.75" customHeight="1"/>
-    <row r="182" ht="15.75" customHeight="1"/>
-    <row r="183" ht="15.75" customHeight="1"/>
-    <row r="184" ht="15.75" customHeight="1"/>
-    <row r="185" ht="15.75" customHeight="1"/>
-    <row r="186" ht="15.75" customHeight="1"/>
-    <row r="187" ht="15.75" customHeight="1"/>
-    <row r="188" ht="15.75" customHeight="1"/>
-    <row r="189" ht="15.75" customHeight="1"/>
-    <row r="190" ht="15.75" customHeight="1"/>
-    <row r="191" ht="15.75" customHeight="1"/>
-    <row r="192" ht="15.75" customHeight="1"/>
-    <row r="193" ht="15.75" customHeight="1"/>
-    <row r="194" ht="15.75" customHeight="1"/>
-    <row r="195" ht="15.75" customHeight="1"/>
-    <row r="196" ht="15.75" customHeight="1"/>
-    <row r="197" ht="15.75" customHeight="1"/>
-    <row r="198" ht="15.75" customHeight="1"/>
-    <row r="199" ht="15.75" customHeight="1"/>
-    <row r="200" ht="15.75" customHeight="1"/>
-    <row r="201" ht="15.75" customHeight="1"/>
-    <row r="202" ht="15.75" customHeight="1"/>
-    <row r="203" ht="15.75" customHeight="1"/>
-    <row r="204" ht="15.75" customHeight="1"/>
-    <row r="205" ht="15.75" customHeight="1"/>
-    <row r="206" ht="15.75" customHeight="1"/>
-    <row r="207" ht="15.75" customHeight="1"/>
-    <row r="208" ht="15.75" customHeight="1"/>
-    <row r="209" ht="15.75" customHeight="1"/>
-    <row r="210" ht="15.75" customHeight="1"/>
-    <row r="211" ht="15.75" customHeight="1"/>
-    <row r="212" ht="15.75" customHeight="1"/>
-    <row r="213" ht="15.75" customHeight="1"/>
-    <row r="214" ht="15.75" customHeight="1"/>
-    <row r="215" ht="15.75" customHeight="1"/>
-    <row r="216" ht="15.75" customHeight="1"/>
-    <row r="217" ht="15.75" customHeight="1"/>
-    <row r="218" ht="15.75" customHeight="1"/>
-    <row r="219" ht="15.75" customHeight="1"/>
-    <row r="220" ht="15.75" customHeight="1"/>
-    <row r="221" ht="15.75" customHeight="1"/>
-    <row r="222" ht="15.75" customHeight="1"/>
-    <row r="223" ht="15.75" customHeight="1"/>
-    <row r="224" ht="15.75" customHeight="1"/>
-    <row r="225" ht="15.75" customHeight="1"/>
-    <row r="226" ht="15.75" customHeight="1"/>
-    <row r="227" ht="15.75" customHeight="1"/>
-    <row r="228" ht="15.75" customHeight="1"/>
-    <row r="229" ht="15.75" customHeight="1"/>
-    <row r="230" ht="15.75" customHeight="1"/>
-    <row r="231" ht="15.75" customHeight="1"/>
-    <row r="232" ht="15.75" customHeight="1"/>
-    <row r="233" ht="15.75" customHeight="1"/>
-    <row r="234" ht="15.75" customHeight="1"/>
-    <row r="235" ht="15.75" customHeight="1"/>
-    <row r="236" ht="15.75" customHeight="1"/>
-    <row r="237" ht="15.75" customHeight="1"/>
-    <row r="238" ht="15.75" customHeight="1"/>
-    <row r="239" ht="15.75" customHeight="1"/>
-    <row r="240" ht="15.75" customHeight="1"/>
-    <row r="241" ht="15.75" customHeight="1"/>
-    <row r="242" ht="15.75" customHeight="1"/>
-    <row r="243" ht="15.75" customHeight="1"/>
-    <row r="244" ht="15.75" customHeight="1"/>
-    <row r="245" ht="15.75" customHeight="1"/>
-    <row r="246" ht="15.75" customHeight="1"/>
-    <row r="247" ht="15.75" customHeight="1"/>
-    <row r="248" ht="15.75" customHeight="1"/>
-    <row r="249" ht="15.75" customHeight="1"/>
-    <row r="250" ht="15.75" customHeight="1"/>
-    <row r="251" ht="15.75" customHeight="1"/>
-    <row r="252" ht="15.75" customHeight="1"/>
-    <row r="253" ht="15.75" customHeight="1"/>
-    <row r="254" ht="15.75" customHeight="1"/>
-    <row r="255" ht="15.75" customHeight="1"/>
-    <row r="256" ht="15.75" customHeight="1"/>
-    <row r="257" ht="15.75" customHeight="1"/>
-    <row r="258" ht="15.75" customHeight="1"/>
-    <row r="259" ht="15.75" customHeight="1"/>
-    <row r="260" ht="15.75" customHeight="1"/>
-    <row r="261" ht="15.75" customHeight="1"/>
-    <row r="262" ht="15.75" customHeight="1"/>
-    <row r="263" ht="15.75" customHeight="1"/>
-    <row r="264" ht="15.75" customHeight="1"/>
-    <row r="265" ht="15.75" customHeight="1"/>
-    <row r="266" ht="15.75" customHeight="1"/>
-    <row r="267" ht="15.75" customHeight="1"/>
-    <row r="268" ht="15.75" customHeight="1"/>
-    <row r="269" ht="15.75" customHeight="1"/>
-    <row r="270" ht="15.75" customHeight="1"/>
-    <row r="271" ht="15.75" customHeight="1"/>
-    <row r="272" ht="15.75" customHeight="1"/>
-    <row r="273" ht="15.75" customHeight="1"/>
-    <row r="274" ht="15.75" customHeight="1"/>
-    <row r="275" ht="15.75" customHeight="1"/>
-    <row r="276" ht="15.75" customHeight="1"/>
-    <row r="277" ht="15.75" customHeight="1"/>
-    <row r="278" ht="15.75" customHeight="1"/>
-    <row r="279" ht="15.75" customHeight="1"/>
-    <row r="280" ht="15.75" customHeight="1"/>
-    <row r="281" ht="15.75" customHeight="1"/>
-    <row r="282" ht="15.75" customHeight="1"/>
-    <row r="283" ht="15.75" customHeight="1"/>
-    <row r="284" ht="15.75" customHeight="1"/>
-    <row r="285" ht="15.75" customHeight="1"/>
-    <row r="286" ht="15.75" customHeight="1"/>
-    <row r="287" ht="15.75" customHeight="1"/>
-    <row r="288" ht="15.75" customHeight="1"/>
-    <row r="289" ht="15.75" customHeight="1"/>
-    <row r="290" ht="15.75" customHeight="1"/>
-    <row r="291" ht="15.75" customHeight="1"/>
-    <row r="292" ht="15.75" customHeight="1"/>
-    <row r="293" ht="15.75" customHeight="1"/>
-    <row r="294" ht="15.75" customHeight="1"/>
-    <row r="295" ht="15.75" customHeight="1"/>
-    <row r="296" ht="15.75" customHeight="1"/>
-    <row r="297" ht="15.75" customHeight="1"/>
-    <row r="298" ht="15.75" customHeight="1"/>
-    <row r="299" ht="15.75" customHeight="1"/>
-    <row r="300" ht="15.75" customHeight="1"/>
-    <row r="301" ht="15.75" customHeight="1"/>
-    <row r="302" ht="15.75" customHeight="1"/>
-    <row r="303" ht="15.75" customHeight="1"/>
-    <row r="304" ht="15.75" customHeight="1"/>
-    <row r="305" ht="15.75" customHeight="1"/>
-    <row r="306" ht="15.75" customHeight="1"/>
-    <row r="307" ht="15.75" customHeight="1"/>
-    <row r="308" ht="15.75" customHeight="1"/>
-    <row r="309" ht="15.75" customHeight="1"/>
-    <row r="310" ht="15.75" customHeight="1"/>
-    <row r="311" ht="15.75" customHeight="1"/>
-    <row r="312" ht="15.75" customHeight="1"/>
-    <row r="313" ht="15.75" customHeight="1"/>
-    <row r="314" ht="15.75" customHeight="1"/>
-    <row r="315" ht="15.75" customHeight="1"/>
-    <row r="316" ht="15.75" customHeight="1"/>
-    <row r="317" ht="15.75" customHeight="1"/>
-    <row r="318" ht="15.75" customHeight="1"/>
-    <row r="319" ht="15.75" customHeight="1"/>
-    <row r="320" ht="15.75" customHeight="1"/>
-    <row r="321" ht="15.75" customHeight="1"/>
-    <row r="322" ht="15.75" customHeight="1"/>
-    <row r="323" ht="15.75" customHeight="1"/>
-    <row r="324" ht="15.75" customHeight="1"/>
-    <row r="325" ht="15.75" customHeight="1"/>
-    <row r="326" ht="15.75" customHeight="1"/>
-    <row r="327" ht="15.75" customHeight="1"/>
-    <row r="328" ht="15.75" customHeight="1"/>
-    <row r="329" ht="15.75" customHeight="1"/>
-    <row r="330" ht="15.75" customHeight="1"/>
-    <row r="331" ht="15.75" customHeight="1"/>
-    <row r="332" ht="15.75" customHeight="1"/>
-    <row r="333" ht="15.75" customHeight="1"/>
-    <row r="334" ht="15.75" customHeight="1"/>
-    <row r="335" ht="15.75" customHeight="1"/>
-    <row r="336" ht="15.75" customHeight="1"/>
-    <row r="337" ht="15.75" customHeight="1"/>
-    <row r="338" ht="15.75" customHeight="1"/>
-    <row r="339" ht="15.75" customHeight="1"/>
-    <row r="340" ht="15.75" customHeight="1"/>
-    <row r="341" ht="15.75" customHeight="1"/>
-    <row r="342" ht="15.75" customHeight="1"/>
-    <row r="343" ht="15.75" customHeight="1"/>
-    <row r="344" ht="15.75" customHeight="1"/>
-    <row r="345" ht="15.75" customHeight="1"/>
-    <row r="346" ht="15.75" customHeight="1"/>
-    <row r="347" ht="15.75" customHeight="1"/>
-    <row r="348" ht="15.75" customHeight="1"/>
-    <row r="349" ht="15.75" customHeight="1"/>
-    <row r="350" ht="15.75" customHeight="1"/>
-    <row r="351" ht="15.75" customHeight="1"/>
-    <row r="352" ht="15.75" customHeight="1"/>
-    <row r="353" ht="15.75" customHeight="1"/>
-    <row r="354" ht="15.75" customHeight="1"/>
-    <row r="355" ht="15.75" customHeight="1"/>
-    <row r="356" ht="15.75" customHeight="1"/>
-    <row r="357" ht="15.75" customHeight="1"/>
-    <row r="358" ht="15.75" customHeight="1"/>
-    <row r="359" ht="15.75" customHeight="1"/>
-    <row r="360" ht="15.75" customHeight="1"/>
-    <row r="361" ht="15.75" customHeight="1"/>
-    <row r="362" ht="15.75" customHeight="1"/>
-    <row r="363" ht="15.75" customHeight="1"/>
-    <row r="364" ht="15.75" customHeight="1"/>
-    <row r="365" ht="15.75" customHeight="1"/>
-    <row r="366" ht="15.75" customHeight="1"/>
-    <row r="367" ht="15.75" customHeight="1"/>
-    <row r="368" ht="15.75" customHeight="1"/>
-    <row r="369" ht="15.75" customHeight="1"/>
-    <row r="370" ht="15.75" customHeight="1"/>
-    <row r="371" ht="15.75" customHeight="1"/>
-    <row r="372" ht="15.75" customHeight="1"/>
-    <row r="373" ht="15.75" customHeight="1"/>
-    <row r="374" ht="15.75" customHeight="1"/>
-    <row r="375" ht="15.75" customHeight="1"/>
-    <row r="376" ht="15.75" customHeight="1"/>
-    <row r="377" ht="15.75" customHeight="1"/>
-    <row r="378" ht="15.75" customHeight="1"/>
-    <row r="379" ht="15.75" customHeight="1"/>
-    <row r="380" ht="15.75" customHeight="1"/>
-    <row r="381" ht="15.75" customHeight="1"/>
-    <row r="382" ht="15.75" customHeight="1"/>
-    <row r="383" ht="15.75" customHeight="1"/>
-    <row r="384" ht="15.75" customHeight="1"/>
-    <row r="385" ht="15.75" customHeight="1"/>
-    <row r="386" ht="15.75" customHeight="1"/>
-    <row r="387" ht="15.75" customHeight="1"/>
-    <row r="388" ht="15.75" customHeight="1"/>
-    <row r="389" ht="15.75" customHeight="1"/>
-    <row r="390" ht="15.75" customHeight="1"/>
-    <row r="391" ht="15.75" customHeight="1"/>
-    <row r="392" ht="15.75" customHeight="1"/>
-    <row r="393" ht="15.75" customHeight="1"/>
-    <row r="394" ht="15.75" customHeight="1"/>
-    <row r="395" ht="15.75" customHeight="1"/>
-    <row r="396" ht="15.75" customHeight="1"/>
-    <row r="397" ht="15.75" customHeight="1"/>
-    <row r="398" ht="15.75" customHeight="1"/>
-    <row r="399" ht="15.75" customHeight="1"/>
-    <row r="400" ht="15.75" customHeight="1"/>
-    <row r="401" ht="15.75" customHeight="1"/>
-    <row r="402" ht="15.75" customHeight="1"/>
-    <row r="403" ht="15.75" customHeight="1"/>
-    <row r="404" ht="15.75" customHeight="1"/>
-    <row r="405" ht="15.75" customHeight="1"/>
-    <row r="406" ht="15.75" customHeight="1"/>
-    <row r="407" ht="15.75" customHeight="1"/>
-    <row r="408" ht="15.75" customHeight="1"/>
-    <row r="409" ht="15.75" customHeight="1"/>
-    <row r="410" ht="15.75" customHeight="1"/>
-    <row r="411" ht="15.75" customHeight="1"/>
-    <row r="412" ht="15.75" customHeight="1"/>
-    <row r="413" ht="15.75" customHeight="1"/>
-    <row r="414" ht="15.75" customHeight="1"/>
-    <row r="415" ht="15.75" customHeight="1"/>
-    <row r="416" ht="15.75" customHeight="1"/>
-    <row r="417" ht="15.75" customHeight="1"/>
-    <row r="418" ht="15.75" customHeight="1"/>
-    <row r="419" ht="15.75" customHeight="1"/>
-    <row r="420" ht="15.75" customHeight="1"/>
-    <row r="421" ht="15.75" customHeight="1"/>
-    <row r="422" ht="15.75" customHeight="1"/>
-    <row r="423" ht="15.75" customHeight="1"/>
-    <row r="424" ht="15.75" customHeight="1"/>
-    <row r="425" ht="15.75" customHeight="1"/>
-    <row r="426" ht="15.75" customHeight="1"/>
-    <row r="427" ht="15.75" customHeight="1"/>
-    <row r="428" ht="15.75" customHeight="1"/>
-    <row r="429" ht="15.75" customHeight="1"/>
-    <row r="430" ht="15.75" customHeight="1"/>
-    <row r="431" ht="15.75" customHeight="1"/>
-    <row r="432" ht="15.75" customHeight="1"/>
-    <row r="433" ht="15.75" customHeight="1"/>
-    <row r="434" ht="15.75" customHeight="1"/>
-    <row r="435" ht="15.75" customHeight="1"/>
-    <row r="436" ht="15.75" customHeight="1"/>
-    <row r="437" ht="15.75" customHeight="1"/>
-    <row r="438" ht="15.75" customHeight="1"/>
-    <row r="439" ht="15.75" customHeight="1"/>
-    <row r="440" ht="15.75" customHeight="1"/>
-    <row r="441" ht="15.75" customHeight="1"/>
-    <row r="442" ht="15.75" customHeight="1"/>
-    <row r="443" ht="15.75" customHeight="1"/>
-    <row r="444" ht="15.75" customHeight="1"/>
-    <row r="445" ht="15.75" customHeight="1"/>
-    <row r="446" ht="15.75" customHeight="1"/>
-    <row r="447" ht="15.75" customHeight="1"/>
-    <row r="448" ht="15.75" customHeight="1"/>
-    <row r="449" ht="15.75" customHeight="1"/>
-    <row r="450" ht="15.75" customHeight="1"/>
-    <row r="451" ht="15.75" customHeight="1"/>
-    <row r="452" ht="15.75" customHeight="1"/>
-    <row r="453" ht="15.75" customHeight="1"/>
-    <row r="454" ht="15.75" customHeight="1"/>
-    <row r="455" ht="15.75" customHeight="1"/>
-    <row r="456" ht="15.75" customHeight="1"/>
-    <row r="457" ht="15.75" customHeight="1"/>
-    <row r="458" ht="15.75" customHeight="1"/>
-    <row r="459" ht="15.75" customHeight="1"/>
-    <row r="460" ht="15.75" customHeight="1"/>
-    <row r="461" ht="15.75" customHeight="1"/>
-    <row r="462" ht="15.75" customHeight="1"/>
-    <row r="463" ht="15.75" customHeight="1"/>
-    <row r="464" ht="15.75" customHeight="1"/>
-    <row r="465" ht="15.75" customHeight="1"/>
-    <row r="466" ht="15.75" customHeight="1"/>
-    <row r="467" ht="15.75" customHeight="1"/>
-    <row r="468" ht="15.75" customHeight="1"/>
-    <row r="469" ht="15.75" customHeight="1"/>
-    <row r="470" ht="15.75" customHeight="1"/>
-    <row r="471" ht="15.75" customHeight="1"/>
-    <row r="472" ht="15.75" customHeight="1"/>
-    <row r="473" ht="15.75" customHeight="1"/>
-    <row r="474" ht="15.75" customHeight="1"/>
-    <row r="475" ht="15.75" customHeight="1"/>
-    <row r="476" ht="15.75" customHeight="1"/>
-    <row r="477" ht="15.75" customHeight="1"/>
-    <row r="478" ht="15.75" customHeight="1"/>
-    <row r="479" ht="15.75" customHeight="1"/>
-    <row r="480" ht="15.75" customHeight="1"/>
-    <row r="481" ht="15.75" customHeight="1"/>
-    <row r="482" ht="15.75" customHeight="1"/>
-    <row r="483" ht="15.75" customHeight="1"/>
-    <row r="484" ht="15.75" customHeight="1"/>
-    <row r="485" ht="15.75" customHeight="1"/>
-    <row r="486" ht="15.75" customHeight="1"/>
-    <row r="487" ht="15.75" customHeight="1"/>
-    <row r="488" ht="15.75" customHeight="1"/>
-    <row r="489" ht="15.75" customHeight="1"/>
-    <row r="490" ht="15.75" customHeight="1"/>
-    <row r="491" ht="15.75" customHeight="1"/>
-    <row r="492" ht="15.75" customHeight="1"/>
-    <row r="493" ht="15.75" customHeight="1"/>
-    <row r="494" ht="15.75" customHeight="1"/>
-    <row r="495" ht="15.75" customHeight="1"/>
-    <row r="496" ht="15.75" customHeight="1"/>
-    <row r="497" ht="15.75" customHeight="1"/>
-    <row r="498" ht="15.75" customHeight="1"/>
-    <row r="499" ht="15.75" customHeight="1"/>
-    <row r="500" ht="15.75" customHeight="1"/>
-    <row r="501" ht="15.75" customHeight="1"/>
-    <row r="502" ht="15.75" customHeight="1"/>
-    <row r="503" ht="15.75" customHeight="1"/>
-    <row r="504" ht="15.75" customHeight="1"/>
-    <row r="505" ht="15.75" customHeight="1"/>
-    <row r="506" ht="15.75" customHeight="1"/>
-    <row r="507" ht="15.75" customHeight="1"/>
-    <row r="508" ht="15.75" customHeight="1"/>
-    <row r="509" ht="15.75" customHeight="1"/>
-    <row r="510" ht="15.75" customHeight="1"/>
-    <row r="511" ht="15.75" customHeight="1"/>
-    <row r="512" ht="15.75" customHeight="1"/>
-    <row r="513" ht="15.75" customHeight="1"/>
-    <row r="514" ht="15.75" customHeight="1"/>
-    <row r="515" ht="15.75" customHeight="1"/>
-    <row r="516" ht="15.75" customHeight="1"/>
-    <row r="517" ht="15.75" customHeight="1"/>
-    <row r="518" ht="15.75" customHeight="1"/>
-    <row r="519" ht="15.75" customHeight="1"/>
-    <row r="520" ht="15.75" customHeight="1"/>
-    <row r="521" ht="15.75" customHeight="1"/>
-    <row r="522" ht="15.75" customHeight="1"/>
-    <row r="523" ht="15.75" customHeight="1"/>
-    <row r="524" ht="15.75" customHeight="1"/>
-    <row r="525" ht="15.75" customHeight="1"/>
-    <row r="526" ht="15.75" customHeight="1"/>
-    <row r="527" ht="15.75" customHeight="1"/>
-    <row r="528" ht="15.75" customHeight="1"/>
-    <row r="529" ht="15.75" customHeight="1"/>
-    <row r="530" ht="15.75" customHeight="1"/>
-    <row r="531" ht="15.75" customHeight="1"/>
-    <row r="532" ht="15.75" customHeight="1"/>
-    <row r="533" ht="15.75" customHeight="1"/>
-    <row r="534" ht="15.75" customHeight="1"/>
-    <row r="535" ht="15.75" customHeight="1"/>
-    <row r="536" ht="15.75" customHeight="1"/>
-    <row r="537" ht="15.75" customHeight="1"/>
-    <row r="538" ht="15.75" customHeight="1"/>
-    <row r="539" ht="15.75" customHeight="1"/>
-    <row r="540" ht="15.75" customHeight="1"/>
-    <row r="541" ht="15.75" customHeight="1"/>
-    <row r="542" ht="15.75" customHeight="1"/>
-    <row r="543" ht="15.75" customHeight="1"/>
-    <row r="544" ht="15.75" customHeight="1"/>
-    <row r="545" ht="15.75" customHeight="1"/>
-    <row r="546" ht="15.75" customHeight="1"/>
-    <row r="547" ht="15.75" customHeight="1"/>
-    <row r="548" ht="15.75" customHeight="1"/>
-    <row r="549" ht="15.75" customHeight="1"/>
-    <row r="550" ht="15.75" customHeight="1"/>
-    <row r="551" ht="15.75" customHeight="1"/>
-    <row r="552" ht="15.75" customHeight="1"/>
-    <row r="553" ht="15.75" customHeight="1"/>
-    <row r="554" ht="15.75" customHeight="1"/>
-    <row r="555" ht="15.75" customHeight="1"/>
-    <row r="556" ht="15.75" customHeight="1"/>
-    <row r="557" ht="15.75" customHeight="1"/>
-    <row r="558" ht="15.75" customHeight="1"/>
-    <row r="559" ht="15.75" customHeight="1"/>
-    <row r="560" ht="15.75" customHeight="1"/>
-    <row r="561" ht="15.75" customHeight="1"/>
-    <row r="562" ht="15.75" customHeight="1"/>
-    <row r="563" ht="15.75" customHeight="1"/>
-    <row r="564" ht="15.75" customHeight="1"/>
-    <row r="565" ht="15.75" customHeight="1"/>
-    <row r="566" ht="15.75" customHeight="1"/>
-    <row r="567" ht="15.75" customHeight="1"/>
-    <row r="568" ht="15.75" customHeight="1"/>
-    <row r="569" ht="15.75" customHeight="1"/>
-    <row r="570" ht="15.75" customHeight="1"/>
-    <row r="571" ht="15.75" customHeight="1"/>
-    <row r="572" ht="15.75" customHeight="1"/>
-    <row r="573" ht="15.75" customHeight="1"/>
-    <row r="574" ht="15.75" customHeight="1"/>
-    <row r="575" ht="15.75" customHeight="1"/>
-    <row r="576" ht="15.75" customHeight="1"/>
-    <row r="577" ht="15.75" customHeight="1"/>
-    <row r="578" ht="15.75" customHeight="1"/>
-    <row r="579" ht="15.75" customHeight="1"/>
-    <row r="580" ht="15.75" customHeight="1"/>
-    <row r="581" ht="15.75" customHeight="1"/>
-    <row r="582" ht="15.75" customHeight="1"/>
-    <row r="583" ht="15.75" customHeight="1"/>
-    <row r="584" ht="15.75" customHeight="1"/>
-    <row r="585" ht="15.75" customHeight="1"/>
-    <row r="586" ht="15.75" customHeight="1"/>
-    <row r="587" ht="15.75" customHeight="1"/>
-    <row r="588" ht="15.75" customHeight="1"/>
-    <row r="589" ht="15.75" customHeight="1"/>
-    <row r="590" ht="15.75" customHeight="1"/>
-    <row r="591" ht="15.75" customHeight="1"/>
-    <row r="592" ht="15.75" customHeight="1"/>
-    <row r="593" ht="15.75" customHeight="1"/>
-    <row r="594" ht="15.75" customHeight="1"/>
-    <row r="595" ht="15.75" customHeight="1"/>
-    <row r="596" ht="15.75" customHeight="1"/>
-    <row r="597" ht="15.75" customHeight="1"/>
-    <row r="598" ht="15.75" customHeight="1"/>
-    <row r="599" ht="15.75" customHeight="1"/>
-    <row r="600" ht="15.75" customHeight="1"/>
-    <row r="601" ht="15.75" customHeight="1"/>
-    <row r="602" ht="15.75" customHeight="1"/>
-    <row r="603" ht="15.75" customHeight="1"/>
-    <row r="604" ht="15.75" customHeight="1"/>
-    <row r="605" ht="15.75" customHeight="1"/>
-    <row r="606" ht="15.75" customHeight="1"/>
-    <row r="607" ht="15.75" customHeight="1"/>
-    <row r="608" ht="15.75" customHeight="1"/>
-    <row r="609" ht="15.75" customHeight="1"/>
-    <row r="610" ht="15.75" customHeight="1"/>
-    <row r="611" ht="15.75" customHeight="1"/>
-    <row r="612" ht="15.75" customHeight="1"/>
-    <row r="613" ht="15.75" customHeight="1"/>
-    <row r="614" ht="15.75" customHeight="1"/>
-    <row r="615" ht="15.75" customHeight="1"/>
-    <row r="616" ht="15.75" customHeight="1"/>
-    <row r="617" ht="15.75" customHeight="1"/>
-    <row r="618" ht="15.75" customHeight="1"/>
-    <row r="619" ht="15.75" customHeight="1"/>
-    <row r="620" ht="15.75" customHeight="1"/>
-    <row r="621" ht="15.75" customHeight="1"/>
-    <row r="622" ht="15.75" customHeight="1"/>
-    <row r="623" ht="15.75" customHeight="1"/>
-    <row r="624" ht="15.75" customHeight="1"/>
-    <row r="625" ht="15.75" customHeight="1"/>
-    <row r="626" ht="15.75" customHeight="1"/>
-    <row r="627" ht="15.75" customHeight="1"/>
-    <row r="628" ht="15.75" customHeight="1"/>
-    <row r="629" ht="15.75" customHeight="1"/>
-    <row r="630" ht="15.75" customHeight="1"/>
-    <row r="631" ht="15.75" customHeight="1"/>
-    <row r="632" ht="15.75" customHeight="1"/>
-    <row r="633" ht="15.75" customHeight="1"/>
-    <row r="634" ht="15.75" customHeight="1"/>
-    <row r="635" ht="15.75" customHeight="1"/>
-    <row r="636" ht="15.75" customHeight="1"/>
-    <row r="637" ht="15.75" customHeight="1"/>
-    <row r="638" ht="15.75" customHeight="1"/>
-    <row r="639" ht="15.75" customHeight="1"/>
-    <row r="640" ht="15.75" customHeight="1"/>
-    <row r="641" ht="15.75" customHeight="1"/>
-    <row r="642" ht="15.75" customHeight="1"/>
-    <row r="643" ht="15.75" customHeight="1"/>
-    <row r="644" ht="15.75" customHeight="1"/>
-    <row r="645" ht="15.75" customHeight="1"/>
-    <row r="646" ht="15.75" customHeight="1"/>
-    <row r="647" ht="15.75" customHeight="1"/>
-    <row r="648" ht="15.75" customHeight="1"/>
-    <row r="649" ht="15.75" customHeight="1"/>
-    <row r="650" ht="15.75" customHeight="1"/>
-    <row r="651" ht="15.75" customHeight="1"/>
-    <row r="652" ht="15.75" customHeight="1"/>
-    <row r="653" ht="15.75" customHeight="1"/>
-    <row r="654" ht="15.75" customHeight="1"/>
-    <row r="655" ht="15.75" customHeight="1"/>
-    <row r="656" ht="15.75" customHeight="1"/>
-    <row r="657" ht="15.75" customHeight="1"/>
-    <row r="658" ht="15.75" customHeight="1"/>
-    <row r="659" ht="15.75" customHeight="1"/>
-    <row r="660" ht="15.75" customHeight="1"/>
-    <row r="661" ht="15.75" customHeight="1"/>
-    <row r="662" ht="15.75" customHeight="1"/>
-    <row r="663" ht="15.75" customHeight="1"/>
-    <row r="664" ht="15.75" customHeight="1"/>
-    <row r="665" ht="15.75" customHeight="1"/>
-    <row r="666" ht="15.75" customHeight="1"/>
-    <row r="667" ht="15.75" customHeight="1"/>
-    <row r="668" ht="15.75" customHeight="1"/>
-    <row r="669" ht="15.75" customHeight="1"/>
-    <row r="670" ht="15.75" customHeight="1"/>
-    <row r="671" ht="15.75" customHeight="1"/>
-    <row r="672" ht="15.75" customHeight="1"/>
-    <row r="673" ht="15.75" customHeight="1"/>
-    <row r="674" ht="15.75" customHeight="1"/>
-    <row r="675" ht="15.75" customHeight="1"/>
-    <row r="676" ht="15.75" customHeight="1"/>
-    <row r="677" ht="15.75" customHeight="1"/>
-    <row r="678" ht="15.75" customHeight="1"/>
-    <row r="679" ht="15.75" customHeight="1"/>
-    <row r="680" ht="15.75" customHeight="1"/>
-    <row r="681" ht="15.75" customHeight="1"/>
-    <row r="682" ht="15.75" customHeight="1"/>
-    <row r="683" ht="15.75" customHeight="1"/>
-    <row r="684" ht="15.75" customHeight="1"/>
-    <row r="685" ht="15.75" customHeight="1"/>
-    <row r="686" ht="15.75" customHeight="1"/>
-    <row r="687" ht="15.75" customHeight="1"/>
-    <row r="688" ht="15.75" customHeight="1"/>
-    <row r="689" ht="15.75" customHeight="1"/>
-    <row r="690" ht="15.75" customHeight="1"/>
-    <row r="691" ht="15.75" customHeight="1"/>
-    <row r="692" ht="15.75" customHeight="1"/>
-    <row r="693" ht="15.75" customHeight="1"/>
-    <row r="694" ht="15.75" customHeight="1"/>
-    <row r="695" ht="15.75" customHeight="1"/>
-    <row r="696" ht="15.75" customHeight="1"/>
-    <row r="697" ht="15.75" customHeight="1"/>
-    <row r="698" ht="15.75" customHeight="1"/>
-    <row r="699" ht="15.75" customHeight="1"/>
-    <row r="700" ht="15.75" customHeight="1"/>
-    <row r="701" ht="15.75" customHeight="1"/>
-    <row r="702" ht="15.75" customHeight="1"/>
-    <row r="703" ht="15.75" customHeight="1"/>
-    <row r="704" ht="15.75" customHeight="1"/>
-    <row r="705" ht="15.75" customHeight="1"/>
-    <row r="706" ht="15.75" customHeight="1"/>
-    <row r="707" ht="15.75" customHeight="1"/>
-    <row r="708" ht="15.75" customHeight="1"/>
-    <row r="709" ht="15.75" customHeight="1"/>
-    <row r="710" ht="15.75" customHeight="1"/>
-    <row r="711" ht="15.75" customHeight="1"/>
-    <row r="712" ht="15.75" customHeight="1"/>
-    <row r="713" ht="15.75" customHeight="1"/>
-    <row r="714" ht="15.75" customHeight="1"/>
-    <row r="715" ht="15.75" customHeight="1"/>
-    <row r="716" ht="15.75" customHeight="1"/>
-    <row r="717" ht="15.75" customHeight="1"/>
-    <row r="718" ht="15.75" customHeight="1"/>
-    <row r="719" ht="15.75" customHeight="1"/>
-    <row r="720" ht="15.75" customHeight="1"/>
-    <row r="721" ht="15.75" customHeight="1"/>
-    <row r="722" ht="15.75" customHeight="1"/>
-    <row r="723" ht="15.75" customHeight="1"/>
-    <row r="724" ht="15.75" customHeight="1"/>
-    <row r="725" ht="15.75" customHeight="1"/>
-    <row r="726" ht="15.75" customHeight="1"/>
-    <row r="727" ht="15.75" customHeight="1"/>
-    <row r="728" ht="15.75" customHeight="1"/>
-    <row r="729" ht="15.75" customHeight="1"/>
-    <row r="730" ht="15.75" customHeight="1"/>
-    <row r="731" ht="15.75" customHeight="1"/>
-    <row r="732" ht="15.75" customHeight="1"/>
-    <row r="733" ht="15.75" customHeight="1"/>
-    <row r="734" ht="15.75" customHeight="1"/>
-    <row r="735" ht="15.75" customHeight="1"/>
-    <row r="736" ht="15.75" customHeight="1"/>
-    <row r="737" ht="15.75" customHeight="1"/>
-    <row r="738" ht="15.75" customHeight="1"/>
-    <row r="739" ht="15.75" customHeight="1"/>
-    <row r="740" ht="15.75" customHeight="1"/>
-    <row r="741" ht="15.75" customHeight="1"/>
-    <row r="742" ht="15.75" customHeight="1"/>
-    <row r="743" ht="15.75" customHeight="1"/>
-    <row r="744" ht="15.75" customHeight="1"/>
-    <row r="745" ht="15.75" customHeight="1"/>
-    <row r="746" ht="15.75" customHeight="1"/>
-    <row r="747" ht="15.75" customHeight="1"/>
-    <row r="748" ht="15.75" customHeight="1"/>
-    <row r="749" ht="15.75" customHeight="1"/>
-    <row r="750" ht="15.75" customHeight="1"/>
-    <row r="751" ht="15.75" customHeight="1"/>
-    <row r="752" ht="15.75" customHeight="1"/>
-    <row r="753" ht="15.75" customHeight="1"/>
-    <row r="754" ht="15.75" customHeight="1"/>
-    <row r="755" ht="15.75" customHeight="1"/>
-    <row r="756" ht="15.75" customHeight="1"/>
-    <row r="757" ht="15.75" customHeight="1"/>
-    <row r="758" ht="15.75" customHeight="1"/>
-    <row r="759" ht="15.75" customHeight="1"/>
-    <row r="760" ht="15.75" customHeight="1"/>
-    <row r="761" ht="15.75" customHeight="1"/>
-    <row r="762" ht="15.75" customHeight="1"/>
-    <row r="763" ht="15.75" customHeight="1"/>
-    <row r="764" ht="15.75" customHeight="1"/>
-    <row r="765" ht="15.75" customHeight="1"/>
-    <row r="766" ht="15.75" customHeight="1"/>
-    <row r="767" ht="15.75" customHeight="1"/>
-    <row r="768" ht="15.75" customHeight="1"/>
-    <row r="769" ht="15.75" customHeight="1"/>
-    <row r="770" ht="15.75" customHeight="1"/>
-    <row r="771" ht="15.75" customHeight="1"/>
-    <row r="772" ht="15.75" customHeight="1"/>
-    <row r="773" ht="15.75" customHeight="1"/>
-    <row r="774" ht="15.75" customHeight="1"/>
-    <row r="775" ht="15.75" customHeight="1"/>
-    <row r="776" ht="15.75" customHeight="1"/>
-    <row r="777" ht="15.75" customHeight="1"/>
-    <row r="778" ht="15.75" customHeight="1"/>
-    <row r="779" ht="15.75" customHeight="1"/>
-    <row r="780" ht="15.75" customHeight="1"/>
-    <row r="781" ht="15.75" customHeight="1"/>
-    <row r="782" ht="15.75" customHeight="1"/>
-    <row r="783" ht="15.75" customHeight="1"/>
-    <row r="784" ht="15.75" customHeight="1"/>
-    <row r="785" ht="15.75" customHeight="1"/>
-    <row r="786" ht="15.75" customHeight="1"/>
-    <row r="787" ht="15.75" customHeight="1"/>
-    <row r="788" ht="15.75" customHeight="1"/>
-    <row r="789" ht="15.75" customHeight="1"/>
-    <row r="790" ht="15.75" customHeight="1"/>
-    <row r="791" ht="15.75" customHeight="1"/>
-    <row r="792" ht="15.75" customHeight="1"/>
-    <row r="793" ht="15.75" customHeight="1"/>
-    <row r="794" ht="15.75" customHeight="1"/>
-    <row r="795" ht="15.75" customHeight="1"/>
-    <row r="796" ht="15.75" customHeight="1"/>
-    <row r="797" ht="15.75" customHeight="1"/>
-    <row r="798" ht="15.75" customHeight="1"/>
-    <row r="799" ht="15.75" customHeight="1"/>
-    <row r="800" ht="15.75" customHeight="1"/>
-    <row r="801" ht="15.75" customHeight="1"/>
-    <row r="802" ht="15.75" customHeight="1"/>
-    <row r="803" ht="15.75" customHeight="1"/>
-    <row r="804" ht="15.75" customHeight="1"/>
-    <row r="805" ht="15.75" customHeight="1"/>
-    <row r="806" ht="15.75" customHeight="1"/>
-    <row r="807" ht="15.75" customHeight="1"/>
-    <row r="808" ht="15.75" customHeight="1"/>
-    <row r="809" ht="15.75" customHeight="1"/>
-    <row r="810" ht="15.75" customHeight="1"/>
-    <row r="811" ht="15.75" customHeight="1"/>
-    <row r="812" ht="15.75" customHeight="1"/>
-    <row r="813" ht="15.75" customHeight="1"/>
-    <row r="814" ht="15.75" customHeight="1"/>
-    <row r="815" ht="15.75" customHeight="1"/>
-    <row r="816" ht="15.75" customHeight="1"/>
-    <row r="817" ht="15.75" customHeight="1"/>
-    <row r="818" ht="15.75" customHeight="1"/>
-    <row r="819" ht="15.75" customHeight="1"/>
-    <row r="820" ht="15.75" customHeight="1"/>
-    <row r="821" ht="15.75" customHeight="1"/>
-    <row r="822" ht="15.75" customHeight="1"/>
-    <row r="823" ht="15.75" customHeight="1"/>
-    <row r="824" ht="15.75" customHeight="1"/>
-    <row r="825" ht="15.75" customHeight="1"/>
-    <row r="826" ht="15.75" customHeight="1"/>
-    <row r="827" ht="15.75" customHeight="1"/>
-    <row r="828" ht="15.75" customHeight="1"/>
-    <row r="829" ht="15.75" customHeight="1"/>
-    <row r="830" ht="15.75" customHeight="1"/>
-    <row r="831" ht="15.75" customHeight="1"/>
-    <row r="832" ht="15.75" customHeight="1"/>
-    <row r="833" ht="15.75" customHeight="1"/>
-    <row r="834" ht="15.75" customHeight="1"/>
-    <row r="835" ht="15.75" customHeight="1"/>
-    <row r="836" ht="15.75" customHeight="1"/>
-    <row r="837" ht="15.75" customHeight="1"/>
-    <row r="838" ht="15.75" customHeight="1"/>
-    <row r="839" ht="15.75" customHeight="1"/>
-    <row r="840" ht="15.75" customHeight="1"/>
-    <row r="841" ht="15.75" customHeight="1"/>
-    <row r="842" ht="15.75" customHeight="1"/>
-    <row r="843" ht="15.75" customHeight="1"/>
-    <row r="844" ht="15.75" customHeight="1"/>
-    <row r="845" ht="15.75" customHeight="1"/>
-    <row r="846" ht="15.75" customHeight="1"/>
-    <row r="847" ht="15.75" customHeight="1"/>
-    <row r="848" ht="15.75" customHeight="1"/>
-    <row r="849" ht="15.75" customHeight="1"/>
-    <row r="850" ht="15.75" customHeight="1"/>
-    <row r="851" ht="15.75" customHeight="1"/>
-    <row r="852" ht="15.75" customHeight="1"/>
-    <row r="853" ht="15.75" customHeight="1"/>
-    <row r="854" ht="15.75" customHeight="1"/>
-    <row r="855" ht="15.75" customHeight="1"/>
-    <row r="856" ht="15.75" customHeight="1"/>
-    <row r="857" ht="15.75" customHeight="1"/>
-    <row r="858" ht="15.75" customHeight="1"/>
-    <row r="859" ht="15.75" customHeight="1"/>
-    <row r="860" ht="15.75" customHeight="1"/>
-    <row r="861" ht="15.75" customHeight="1"/>
-    <row r="862" ht="15.75" customHeight="1"/>
-    <row r="863" ht="15.75" customHeight="1"/>
-    <row r="864" ht="15.75" customHeight="1"/>
-    <row r="865" ht="15.75" customHeight="1"/>
-    <row r="866" ht="15.75" customHeight="1"/>
-    <row r="867" ht="15.75" customHeight="1"/>
-    <row r="868" ht="15.75" customHeight="1"/>
-    <row r="869" ht="15.75" customHeight="1"/>
-    <row r="870" ht="15.75" customHeight="1"/>
-    <row r="871" ht="15.75" customHeight="1"/>
-    <row r="872" ht="15.75" customHeight="1"/>
-    <row r="873" ht="15.75" customHeight="1"/>
-    <row r="874" ht="15.75" customHeight="1"/>
-    <row r="875" ht="15.75" customHeight="1"/>
-    <row r="876" ht="15.75" customHeight="1"/>
-    <row r="877" ht="15.75" customHeight="1"/>
-    <row r="878" ht="15.75" customHeight="1"/>
-    <row r="879" ht="15.75" customHeight="1"/>
-    <row r="880" ht="15.75" customHeight="1"/>
-    <row r="881" ht="15.75" customHeight="1"/>
-    <row r="882" ht="15.75" customHeight="1"/>
-    <row r="883" ht="15.75" customHeight="1"/>
-    <row r="884" ht="15.75" customHeight="1"/>
-    <row r="885" ht="15.75" customHeight="1"/>
-    <row r="886" ht="15.75" customHeight="1"/>
-    <row r="887" ht="15.75" customHeight="1"/>
-    <row r="888" ht="15.75" customHeight="1"/>
-    <row r="889" ht="15.75" customHeight="1"/>
-    <row r="890" ht="15.75" customHeight="1"/>
-    <row r="891" ht="15.75" customHeight="1"/>
-    <row r="892" ht="15.75" customHeight="1"/>
-    <row r="893" ht="15.75" customHeight="1"/>
-    <row r="894" ht="15.75" customHeight="1"/>
-    <row r="895" ht="15.75" customHeight="1"/>
-    <row r="896" ht="15.75" customHeight="1"/>
-    <row r="897" ht="15.75" customHeight="1"/>
-    <row r="898" ht="15.75" customHeight="1"/>
-    <row r="899" ht="15.75" customHeight="1"/>
-    <row r="900" ht="15.75" customHeight="1"/>
-    <row r="901" ht="15.75" customHeight="1"/>
-    <row r="902" ht="15.75" customHeight="1"/>
-    <row r="903" ht="15.75" customHeight="1"/>
-    <row r="904" ht="15.75" customHeight="1"/>
-    <row r="905" ht="15.75" customHeight="1"/>
-    <row r="906" ht="15.75" customHeight="1"/>
-    <row r="907" ht="15.75" customHeight="1"/>
-    <row r="908" ht="15.75" customHeight="1"/>
-    <row r="909" ht="15.75" customHeight="1"/>
-    <row r="910" ht="15.75" customHeight="1"/>
-    <row r="911" ht="15.75" customHeight="1"/>
-    <row r="912" ht="15.75" customHeight="1"/>
-    <row r="913" ht="15.75" customHeight="1"/>
-    <row r="914" ht="15.75" customHeight="1"/>
-    <row r="915" ht="15.75" customHeight="1"/>
-    <row r="916" ht="15.75" customHeight="1"/>
-    <row r="917" ht="15.75" customHeight="1"/>
-    <row r="918" ht="15.75" customHeight="1"/>
-    <row r="919" ht="15.75" customHeight="1"/>
-    <row r="920" ht="15.75" customHeight="1"/>
-    <row r="921" ht="15.75" customHeight="1"/>
-    <row r="922" ht="15.75" customHeight="1"/>
-    <row r="923" ht="15.75" customHeight="1"/>
-    <row r="924" ht="15.75" customHeight="1"/>
-    <row r="925" ht="15.75" customHeight="1"/>
-    <row r="926" ht="15.75" customHeight="1"/>
-    <row r="927" ht="15.75" customHeight="1"/>
-    <row r="928" ht="15.75" customHeight="1"/>
-    <row r="929" ht="15.75" customHeight="1"/>
-    <row r="930" ht="15.75" customHeight="1"/>
-    <row r="931" ht="15.75" customHeight="1"/>
-    <row r="932" ht="15.75" customHeight="1"/>
-    <row r="933" ht="15.75" customHeight="1"/>
-    <row r="934" ht="15.75" customHeight="1"/>
-    <row r="935" ht="15.75" customHeight="1"/>
-    <row r="936" ht="15.75" customHeight="1"/>
-    <row r="937" ht="15.75" customHeight="1"/>
-    <row r="938" ht="15.75" customHeight="1"/>
-    <row r="939" ht="15.75" customHeight="1"/>
-    <row r="940" ht="15.75" customHeight="1"/>
-    <row r="941" ht="15.75" customHeight="1"/>
-    <row r="942" ht="15.75" customHeight="1"/>
-    <row r="943" ht="15.75" customHeight="1"/>
-    <row r="944" ht="15.75" customHeight="1"/>
-    <row r="945" ht="15.75" customHeight="1"/>
-    <row r="946" ht="15.75" customHeight="1"/>
-    <row r="947" ht="15.75" customHeight="1"/>
-    <row r="948" ht="15.75" customHeight="1"/>
-    <row r="949" ht="15.75" customHeight="1"/>
-    <row r="950" ht="15.75" customHeight="1"/>
-    <row r="951" ht="15.75" customHeight="1"/>
-    <row r="952" ht="15.75" customHeight="1"/>
-    <row r="953" ht="15.75" customHeight="1"/>
-    <row r="954" ht="15.75" customHeight="1"/>
-    <row r="955" ht="15.75" customHeight="1"/>
-    <row r="956" ht="15.75" customHeight="1"/>
-    <row r="957" ht="15.75" customHeight="1"/>
-    <row r="958" ht="15.75" customHeight="1"/>
-    <row r="959" ht="15.75" customHeight="1"/>
-    <row r="960" ht="15.75" customHeight="1"/>
-    <row r="961" ht="15.75" customHeight="1"/>
-    <row r="962" ht="15.75" customHeight="1"/>
-    <row r="963" ht="15.75" customHeight="1"/>
-    <row r="964" ht="15.75" customHeight="1"/>
-    <row r="965" ht="15.75" customHeight="1"/>
-    <row r="966" ht="15.75" customHeight="1"/>
-    <row r="967" ht="15.75" customHeight="1"/>
-    <row r="968" ht="15.75" customHeight="1"/>
-    <row r="969" ht="15.75" customHeight="1"/>
-    <row r="970" ht="15.75" customHeight="1"/>
-    <row r="971" ht="15.75" customHeight="1"/>
-    <row r="972" ht="15.75" customHeight="1"/>
-    <row r="973" ht="15.75" customHeight="1"/>
-    <row r="974" ht="15.75" customHeight="1"/>
-    <row r="975" ht="15.75" customHeight="1"/>
-    <row r="976" ht="15.75" customHeight="1"/>
-    <row r="977" ht="15.75" customHeight="1"/>
-    <row r="978" ht="15.75" customHeight="1"/>
-    <row r="979" ht="15.75" customHeight="1"/>
-    <row r="980" ht="15.75" customHeight="1"/>
-    <row r="981" ht="15.75" customHeight="1"/>
-    <row r="982" ht="15.75" customHeight="1"/>
-    <row r="983" ht="15.75" customHeight="1"/>
-    <row r="984" ht="15.75" customHeight="1"/>
-    <row r="985" ht="15.75" customHeight="1"/>
-    <row r="986" ht="15.75" customHeight="1"/>
-    <row r="987" ht="15.75" customHeight="1"/>
-    <row r="988" ht="15.75" customHeight="1"/>
-    <row r="989" ht="15.75" customHeight="1"/>
-    <row r="990" ht="15.75" customHeight="1"/>
-    <row r="991" ht="15.75" customHeight="1"/>
-    <row r="992" ht="15.75" customHeight="1"/>
-    <row r="993" ht="15.75" customHeight="1"/>
-    <row r="994" ht="15.75" customHeight="1"/>
-    <row r="995" ht="15.75" customHeight="1"/>
-    <row r="996" ht="15.75" customHeight="1"/>
-    <row r="997" ht="15.75" customHeight="1"/>
-    <row r="998" ht="15.75" customHeight="1"/>
-    <row r="999" ht="15.75" customHeight="1"/>
-    <row r="1000" ht="15.75" customHeight="1"/>
-    <row r="1001" ht="15.75" customHeight="1"/>
-    <row r="1002" ht="15.75" customHeight="1"/>
+    <row r="66" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="67" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="68" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="69" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="70" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="71" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="72" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="73" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="74" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="75" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="76" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="77" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="78" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="79" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="80" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="81" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="82" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="83" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="84" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="85" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="86" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="87" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="88" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="89" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="90" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="91" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="92" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="93" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="94" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="95" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="96" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="97" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="98" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="99" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="100" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="101" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="102" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="103" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="104" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="105" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="106" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="107" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="108" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="109" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="110" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="111" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="112" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="113" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="114" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="115" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="116" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="117" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="118" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="119" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="120" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="121" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="122" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="123" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="124" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="125" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="126" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="127" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="128" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="129" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="130" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="131" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="132" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="133" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="134" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="135" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="136" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="137" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="138" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="139" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="140" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="141" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="142" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="143" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="144" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="145" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="146" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="147" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="148" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="149" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="150" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="151" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="152" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="153" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="154" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="155" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="156" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="157" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="158" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="159" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="160" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="161" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="162" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="163" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="164" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="165" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="166" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="167" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="168" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="169" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="170" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="171" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="172" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="173" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="174" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="175" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="176" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="177" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="178" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="179" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="180" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="181" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="182" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="183" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="184" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="185" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="186" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="187" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="188" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="189" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="190" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="191" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="192" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="193" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="194" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="195" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="196" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="197" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="198" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="199" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="200" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="201" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="202" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="203" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="204" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="205" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="206" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="207" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="208" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="209" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="210" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="211" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="212" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="213" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="214" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="215" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="216" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="217" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="218" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="219" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="220" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="221" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="222" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="223" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="224" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="225" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="226" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="227" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="228" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="229" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="230" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="231" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="232" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="233" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="234" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="235" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="236" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="237" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="238" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="239" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="240" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="241" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="242" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="243" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="244" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="245" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="246" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="247" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="248" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="249" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="250" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="251" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="252" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="253" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="254" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="255" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="256" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="257" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="258" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="259" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="260" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="261" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="262" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="263" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="264" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="265" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="266" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="267" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="268" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="269" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="270" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="271" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="272" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="273" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="274" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="275" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="276" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="277" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="278" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="279" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="280" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="281" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="282" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="283" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="284" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="285" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="286" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="287" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="288" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="289" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="290" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="291" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="292" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="293" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="294" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="295" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="296" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="297" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="298" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="299" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="300" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="301" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="302" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="303" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="304" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="305" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="306" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="307" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="308" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="309" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="310" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="311" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="312" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="313" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="314" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="315" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="316" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="317" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="318" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="319" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="320" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="321" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="322" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="323" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="324" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="325" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="326" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="327" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="328" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="329" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="330" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="331" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="332" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="333" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="334" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="335" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="336" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="337" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="338" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="339" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="340" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="341" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="342" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="343" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="344" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="345" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="346" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="347" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="348" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="349" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="350" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="351" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="352" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="353" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="354" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="355" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="356" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="357" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="358" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="359" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="360" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="361" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="362" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="363" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="364" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="365" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="366" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="367" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="368" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="369" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="370" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="371" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="372" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="373" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="374" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="375" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="376" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="377" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="378" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="379" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="380" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="381" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="382" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="383" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="384" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="385" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="386" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="387" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="388" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="389" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="390" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="391" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="392" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="393" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="394" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="395" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="396" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="397" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="398" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="399" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="400" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="401" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="402" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="403" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="404" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="405" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="406" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="407" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="408" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="409" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="410" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="411" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="412" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="413" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="414" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="415" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="416" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="417" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="418" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="419" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="420" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="421" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="422" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="423" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="424" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="425" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="426" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="427" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="428" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="429" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="430" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="431" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="432" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="433" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="434" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="435" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="436" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="437" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="438" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="439" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="440" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="441" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="442" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="443" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="444" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="445" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="446" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="447" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="448" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="449" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="450" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="451" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="452" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="453" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="454" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="455" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="456" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="457" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="458" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="459" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="460" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="461" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="462" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="463" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="464" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="465" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="466" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="467" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="468" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="469" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="470" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="471" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="472" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="473" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="474" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="475" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="476" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="477" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="478" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="479" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="480" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="481" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="482" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="483" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="484" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="485" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="486" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="487" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="488" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="489" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="490" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="491" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="492" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="493" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="494" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="495" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="496" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="497" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="498" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="499" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="500" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="501" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="502" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="503" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="504" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="505" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="506" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="507" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="508" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="509" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="510" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="511" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="512" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="513" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="514" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="515" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="516" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="517" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="518" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="519" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="520" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="521" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="522" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="523" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="524" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="525" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="526" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="527" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="528" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="529" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="530" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="531" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="532" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="533" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="534" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="535" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="536" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="537" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="538" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="539" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="540" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="541" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="542" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="543" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="544" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="545" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="546" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="547" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="548" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="549" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="550" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="551" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="552" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="553" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="554" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="555" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="556" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="557" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="558" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="559" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="560" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="561" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="562" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="563" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="564" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="565" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="566" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="567" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="568" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="569" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="570" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="571" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="572" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="573" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="574" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="575" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="576" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="577" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="578" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="579" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="580" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="581" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="582" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="583" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="584" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="585" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="586" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="587" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="588" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="589" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="590" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="591" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="592" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="593" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="594" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="595" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="596" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="597" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="598" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="599" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="600" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="601" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="602" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="603" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="604" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="605" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="606" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="607" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="608" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="609" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="610" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="611" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="612" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="613" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="614" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="615" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="616" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="617" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="618" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="619" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="620" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="621" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="622" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="623" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="624" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="625" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="626" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="627" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="628" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="629" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="630" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="631" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="632" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="633" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="634" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="635" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="636" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="637" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="638" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="639" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="640" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="641" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="642" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="643" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="644" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="645" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="646" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="647" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="648" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="649" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="650" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="651" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="652" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="653" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="654" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="655" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="656" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="657" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="658" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="659" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="660" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="661" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="662" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="663" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="664" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="665" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="666" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="667" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="668" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="669" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="670" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="671" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="672" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="673" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="674" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="675" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="676" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="677" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="678" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="679" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="680" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="681" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="682" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="683" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="684" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="685" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="686" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="687" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="688" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="689" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="690" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="691" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="692" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="693" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="694" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="695" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="696" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="697" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="698" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="699" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="700" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="701" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="702" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="703" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="704" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="705" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="706" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="707" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="708" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="709" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="710" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="711" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="712" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="713" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="714" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="715" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="716" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="717" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="718" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="719" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="720" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="721" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="722" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="723" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="724" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="725" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="726" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="727" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="728" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="729" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="730" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="731" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="732" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="733" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="734" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="735" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="736" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="737" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="738" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="739" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="740" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="741" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="742" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="743" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="744" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="745" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="746" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="747" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="748" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="749" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="750" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="751" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="752" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="753" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="754" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="755" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="756" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="757" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="758" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="759" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="760" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="761" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="762" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="763" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="764" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="765" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="766" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="767" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="768" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="769" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="770" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="771" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="772" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="773" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="774" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="775" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="776" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="777" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="778" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="779" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="780" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="781" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="782" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="783" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="784" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="785" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="786" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="787" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="788" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="789" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="790" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="791" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="792" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="793" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="794" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="795" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="796" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="797" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="798" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="799" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="800" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="801" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="802" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="803" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="804" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="805" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="806" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="807" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="808" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="809" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="810" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="811" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="812" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="813" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="814" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="815" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="816" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="817" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="818" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="819" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="820" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="821" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="822" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="823" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="824" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="825" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="826" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="827" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="828" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="829" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="830" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="831" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="832" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="833" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="834" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="835" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="836" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="837" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="838" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="839" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="840" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="841" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="842" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="843" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="844" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="845" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="846" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="847" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="848" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="849" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="850" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="851" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="852" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="853" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="854" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="855" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="856" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="857" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="858" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="859" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="860" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="861" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="862" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="863" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="864" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="865" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="866" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="867" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="868" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="869" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="870" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="871" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="872" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="873" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="874" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="875" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="876" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="877" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="878" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="879" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="880" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="881" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="882" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="883" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="884" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="885" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="886" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="887" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="888" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="889" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="890" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="891" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="892" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="893" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="894" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="895" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="896" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="897" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="898" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="899" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="900" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="901" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="902" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="903" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="904" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="905" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="906" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="907" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="908" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="909" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="910" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="911" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="912" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="913" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="914" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="915" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="916" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="917" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="918" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="919" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="920" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="921" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="922" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="923" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="924" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="925" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="926" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="927" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="928" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="929" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="930" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="931" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="932" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="933" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="934" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="935" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="936" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="937" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="938" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="939" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="940" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="941" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="942" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="943" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="944" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="945" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="946" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="947" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="948" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="949" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="950" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="951" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="952" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="953" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="954" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="955" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="956" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="957" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="958" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="959" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="960" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="961" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="962" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="963" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="964" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="965" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="966" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="967" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="968" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="969" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="970" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="971" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="972" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="973" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="974" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="975" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="976" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="977" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="978" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="979" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="980" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="981" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="982" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="983" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="984" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="985" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="986" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="987" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="988" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="989" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="990" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="991" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="992" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="993" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="994" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="995" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="996" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="997" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="998" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="999" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="1000" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="1001" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="1002" spans="1:26" customHeight="1" ht="15.75"/>
   </sheetData>
-  <autoFilter ref="$A$1:$M$66"/>
-  <printOptions/>
-  <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <autoFilter ref="A1:M66"/>
+  <printOptions gridLines="false" gridLinesSet="true"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
   <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
+  <legacyDrawing r:id="rId_comments_vml1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <pageSetUpPr/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <dimension ref="A1:Z1000"/>
+  <sheetFormatPr customHeight="true" defaultRowHeight="15" defaultColWidth="14.43" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="20.0"/>
-    <col customWidth="1" min="2" max="2" width="17.29"/>
-    <col customWidth="1" min="3" max="3" width="14.71"/>
-    <col customWidth="1" min="4" max="4" width="15.57"/>
-    <col customWidth="1" min="6" max="6" width="13.71"/>
-    <col customWidth="1" min="7" max="7" width="14.0"/>
-    <col customWidth="1" min="8" max="10" width="11.0"/>
-    <col customWidth="1" min="11" max="26" width="8.71"/>
+    <col min="1" max="1" width="20" customWidth="true" style="0"/>
+    <col min="2" max="2" width="17.29" customWidth="true" style="0"/>
+    <col min="3" max="3" width="14.71" customWidth="true" style="0"/>
+    <col min="4" max="4" width="15.57" customWidth="true" style="0"/>
+    <col min="6" max="6" width="13.71" customWidth="true" style="0"/>
+    <col min="7" max="7" width="14" customWidth="true" style="0"/>
+    <col min="8" max="8" width="11" customWidth="true" style="0"/>
+    <col min="9" max="9" width="11" customWidth="true" style="0"/>
+    <col min="10" max="10" width="11" customWidth="true" style="0"/>
+    <col min="11" max="11" width="8.71" customWidth="true" style="0"/>
+    <col min="12" max="12" width="8.71" customWidth="true" style="0"/>
+    <col min="13" max="13" width="8.71" customWidth="true" style="0"/>
+    <col min="14" max="14" width="8.71" customWidth="true" style="0"/>
+    <col min="15" max="15" width="8.71" customWidth="true" style="0"/>
+    <col min="16" max="16" width="8.71" customWidth="true" style="0"/>
+    <col min="17" max="17" width="8.71" customWidth="true" style="0"/>
+    <col min="18" max="18" width="8.71" customWidth="true" style="0"/>
+    <col min="19" max="19" width="8.71" customWidth="true" style="0"/>
+    <col min="20" max="20" width="8.71" customWidth="true" style="0"/>
+    <col min="21" max="21" width="8.71" customWidth="true" style="0"/>
+    <col min="22" max="22" width="8.71" customWidth="true" style="0"/>
+    <col min="23" max="23" width="8.71" customWidth="true" style="0"/>
+    <col min="24" max="24" width="8.71" customWidth="true" style="0"/>
+    <col min="25" max="25" width="8.71" customWidth="true" style="0"/>
+    <col min="26" max="26" width="8.71" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:26">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -4087,7 +4162,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:26">
       <c r="A2" s="13" t="s">
         <v>18</v>
       </c>
@@ -4100,7 +4175,7 @@
       </c>
       <c r="D2" s="9">
         <f>SUMIF('Alocări'!$C$2:$C$61,$A2,'Alocări'!F$2:F$61)</f>
-        <v>117.2</v>
+        <v>117.19999999999999</v>
       </c>
       <c r="E2" s="5">
         <f>SUMIF('Alocări'!$C$2:$C$61,$A2,'Alocări'!G$2:G$61)</f>
@@ -4127,7 +4202,7 @@
         <v>51.7</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:26">
       <c r="A3" s="13" t="s">
         <v>19</v>
       </c>
@@ -4167,7 +4242,7 @@
         <v>65.7</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:26">
       <c r="A4" s="13" t="s">
         <v>45</v>
       </c>
@@ -4176,11 +4251,11 @@
       </c>
       <c r="C4" s="9">
         <f>SUMIF('Alocări'!$C$2:$C$61,$A4,'Alocări'!E$2:E$61)</f>
-        <v>88.4</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="D4" s="9">
         <f>SUMIF('Alocări'!$C$2:$C$61,$A4,'Alocări'!F$2:F$61)</f>
-        <v>79.6</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="E4" s="5">
         <f>SUMIF('Alocări'!$C$2:$C$61,$A4,'Alocări'!G$2:G$61)</f>
@@ -4207,7 +4282,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:26">
       <c r="A5" s="13" t="s">
         <v>38</v>
       </c>
@@ -4223,10 +4298,10 @@
         <v>103.5</v>
       </c>
       <c r="E5" s="5">
-        <v>80.0</v>
+        <v>85</v>
       </c>
       <c r="F5" s="5">
-        <v>80.0</v>
+        <v>0</v>
       </c>
       <c r="G5" s="5">
         <f>SUMIF('Alocări'!$C$2:$C$61,$A5,'Alocări'!I$2:I$61)</f>
@@ -4245,7 +4320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:26">
       <c r="A6" s="13" t="s">
         <v>33</v>
       </c>
@@ -4285,7 +4360,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:26">
       <c r="A7" s="13" t="s">
         <v>27</v>
       </c>
@@ -4294,15 +4369,15 @@
       </c>
       <c r="C7" s="9">
         <f>SUMIF('Alocări'!$C$2:$C$61,$A7,'Alocări'!E$2:E$61)</f>
-        <v>131.1</v>
+        <v>131.099999999999994</v>
       </c>
       <c r="D7" s="9">
         <f>SUMIF('Alocări'!$C$2:$C$61,$A7,'Alocări'!F$2:F$61)</f>
-        <v>131.1</v>
+        <v>131.099999999999994</v>
       </c>
       <c r="E7" s="5">
         <f>SUMIF('Alocări'!$C$2:$C$61,$A7,'Alocări'!G$2:G$61)</f>
-        <v>107.6</v>
+        <v>107.59999999999999</v>
       </c>
       <c r="F7" s="5">
         <f>SUMIF('Alocări'!$C$2:$C$61,$A7,'Alocări'!H$2:H$61)</f>
@@ -4325,7 +4400,7 @@
         <v>106.3</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:26">
       <c r="A8" s="13" t="s">
         <v>57</v>
       </c>
@@ -4365,7 +4440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:26">
       <c r="A9" s="13" t="s">
         <v>40</v>
       </c>
@@ -4405,7 +4480,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:26">
       <c r="A10" s="13" t="s">
         <v>21</v>
       </c>
@@ -4422,7 +4497,7 @@
       </c>
       <c r="E10" s="5">
         <f>SUMIF('Alocări'!$C$2:$C$61,$A10,'Alocări'!G$2:G$61)</f>
-        <v>185.7</v>
+        <v>185.69999999999999</v>
       </c>
       <c r="F10" s="5">
         <f>SUMIF('Alocări'!$C$2:$C$61,$A10,'Alocări'!H$2:H$61)</f>
@@ -4445,7 +4520,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:26">
       <c r="A11" s="13" t="s">
         <v>23</v>
       </c>
@@ -4454,11 +4529,11 @@
       </c>
       <c r="C11" s="9">
         <f>SUMIF('Alocări'!$C$2:$C$61,$A11,'Alocări'!E$2:E$61)</f>
-        <v>62.1</v>
+        <v>62.099999999999994</v>
       </c>
       <c r="D11" s="9">
         <f>SUMIF('Alocări'!$C$2:$C$61,$A11,'Alocări'!F$2:F$61)</f>
-        <v>62.1</v>
+        <v>62.099999999999994</v>
       </c>
       <c r="E11" s="5">
         <f>SUMIF('Alocări'!$C$2:$C$61,$A11,'Alocări'!G$2:G$61)</f>
@@ -4485,7 +4560,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:26">
       <c r="A12" s="13" t="s">
         <v>29</v>
       </c>
@@ -4525,7 +4600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:26">
       <c r="A13" s="13" t="s">
         <v>42</v>
       </c>
@@ -4534,7 +4609,7 @@
       </c>
       <c r="C13" s="9">
         <f>SUMIF('Alocări'!$C$2:$C$61,$A13,'Alocări'!E$2:E$61)</f>
-        <v>96.6</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="D13" s="9">
         <f>SUMIF('Alocări'!$C$2:$C$61,$A13,'Alocări'!F$2:F$61)</f>
@@ -4565,7 +4640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:26">
       <c r="A14" s="13" t="s">
         <v>49</v>
       </c>
@@ -4605,7 +4680,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:26">
       <c r="A15" s="13" t="s">
         <v>34</v>
       </c>
@@ -4645,7 +4720,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:26">
       <c r="A16" s="13" t="s">
         <v>14</v>
       </c>
@@ -4662,7 +4737,7 @@
       </c>
       <c r="E16" s="5">
         <f>SUMIF('Alocări'!$C$2:$C$61,$A16,'Alocări'!G$2:G$61)</f>
-        <v>153.7</v>
+        <v>153.69999999999999</v>
       </c>
       <c r="F16" s="5">
         <f>SUMIF('Alocări'!$C$2:$C$61,$A16,'Alocări'!H$2:H$61)</f>
@@ -4685,1003 +4760,1003 @@
         <v>113.7</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:26">
       <c r="E17" s="14"/>
       <c r="F17" s="14"/>
       <c r="G17" s="14"/>
     </row>
-    <row r="18">
+    <row r="18" spans="1:26">
       <c r="E18" s="14"/>
       <c r="F18" s="14"/>
       <c r="G18" s="14"/>
     </row>
-    <row r="19">
+    <row r="19" spans="1:26">
       <c r="E19" s="15"/>
     </row>
-    <row r="21" ht="15.75" customHeight="1"/>
-    <row r="22" ht="15.75" customHeight="1"/>
-    <row r="23" ht="15.75" customHeight="1"/>
-    <row r="24" ht="15.75" customHeight="1"/>
-    <row r="25" ht="15.75" customHeight="1"/>
-    <row r="26" ht="15.75" customHeight="1"/>
-    <row r="27" ht="15.75" customHeight="1"/>
-    <row r="28" ht="15.75" customHeight="1"/>
-    <row r="29" ht="15.75" customHeight="1"/>
-    <row r="30" ht="15.75" customHeight="1"/>
-    <row r="31" ht="15.75" customHeight="1"/>
-    <row r="32" ht="15.75" customHeight="1"/>
-    <row r="33" ht="15.75" customHeight="1"/>
-    <row r="34" ht="15.75" customHeight="1"/>
-    <row r="35" ht="15.75" customHeight="1"/>
-    <row r="36" ht="15.75" customHeight="1"/>
-    <row r="37" ht="15.75" customHeight="1"/>
-    <row r="38" ht="15.75" customHeight="1"/>
-    <row r="39" ht="15.75" customHeight="1"/>
-    <row r="40" ht="15.75" customHeight="1"/>
-    <row r="41" ht="15.75" customHeight="1"/>
-    <row r="42" ht="15.75" customHeight="1"/>
-    <row r="43" ht="15.75" customHeight="1"/>
-    <row r="44" ht="15.75" customHeight="1"/>
-    <row r="45" ht="15.75" customHeight="1"/>
-    <row r="46" ht="15.75" customHeight="1"/>
-    <row r="47" ht="15.75" customHeight="1"/>
-    <row r="48" ht="15.75" customHeight="1"/>
-    <row r="49" ht="15.75" customHeight="1"/>
-    <row r="50" ht="15.75" customHeight="1"/>
-    <row r="51" ht="15.75" customHeight="1"/>
-    <row r="52" ht="15.75" customHeight="1"/>
-    <row r="53" ht="15.75" customHeight="1"/>
-    <row r="54" ht="15.75" customHeight="1"/>
-    <row r="55" ht="15.75" customHeight="1"/>
-    <row r="56" ht="15.75" customHeight="1"/>
-    <row r="57" ht="15.75" customHeight="1"/>
-    <row r="58" ht="15.75" customHeight="1"/>
-    <row r="59" ht="15.75" customHeight="1"/>
-    <row r="60" ht="15.75" customHeight="1"/>
-    <row r="61" ht="15.75" customHeight="1"/>
-    <row r="62" ht="15.75" customHeight="1"/>
-    <row r="63" ht="15.75" customHeight="1"/>
-    <row r="64" ht="15.75" customHeight="1"/>
-    <row r="65" ht="15.75" customHeight="1"/>
-    <row r="66" ht="15.75" customHeight="1"/>
-    <row r="67" ht="15.75" customHeight="1"/>
-    <row r="68" ht="15.75" customHeight="1"/>
-    <row r="69" ht="15.75" customHeight="1"/>
-    <row r="70" ht="15.75" customHeight="1"/>
-    <row r="71" ht="15.75" customHeight="1"/>
-    <row r="72" ht="15.75" customHeight="1"/>
-    <row r="73" ht="15.75" customHeight="1"/>
-    <row r="74" ht="15.75" customHeight="1"/>
-    <row r="75" ht="15.75" customHeight="1"/>
-    <row r="76" ht="15.75" customHeight="1"/>
-    <row r="77" ht="15.75" customHeight="1"/>
-    <row r="78" ht="15.75" customHeight="1"/>
-    <row r="79" ht="15.75" customHeight="1"/>
-    <row r="80" ht="15.75" customHeight="1"/>
-    <row r="81" ht="15.75" customHeight="1"/>
-    <row r="82" ht="15.75" customHeight="1"/>
-    <row r="83" ht="15.75" customHeight="1"/>
-    <row r="84" ht="15.75" customHeight="1"/>
-    <row r="85" ht="15.75" customHeight="1"/>
-    <row r="86" ht="15.75" customHeight="1"/>
-    <row r="87" ht="15.75" customHeight="1"/>
-    <row r="88" ht="15.75" customHeight="1"/>
-    <row r="89" ht="15.75" customHeight="1"/>
-    <row r="90" ht="15.75" customHeight="1"/>
-    <row r="91" ht="15.75" customHeight="1"/>
-    <row r="92" ht="15.75" customHeight="1"/>
-    <row r="93" ht="15.75" customHeight="1"/>
-    <row r="94" ht="15.75" customHeight="1"/>
-    <row r="95" ht="15.75" customHeight="1"/>
-    <row r="96" ht="15.75" customHeight="1"/>
-    <row r="97" ht="15.75" customHeight="1"/>
-    <row r="98" ht="15.75" customHeight="1"/>
-    <row r="99" ht="15.75" customHeight="1"/>
-    <row r="100" ht="15.75" customHeight="1"/>
-    <row r="101" ht="15.75" customHeight="1"/>
-    <row r="102" ht="15.75" customHeight="1"/>
-    <row r="103" ht="15.75" customHeight="1"/>
-    <row r="104" ht="15.75" customHeight="1"/>
-    <row r="105" ht="15.75" customHeight="1"/>
-    <row r="106" ht="15.75" customHeight="1"/>
-    <row r="107" ht="15.75" customHeight="1"/>
-    <row r="108" ht="15.75" customHeight="1"/>
-    <row r="109" ht="15.75" customHeight="1"/>
-    <row r="110" ht="15.75" customHeight="1"/>
-    <row r="111" ht="15.75" customHeight="1"/>
-    <row r="112" ht="15.75" customHeight="1"/>
-    <row r="113" ht="15.75" customHeight="1"/>
-    <row r="114" ht="15.75" customHeight="1"/>
-    <row r="115" ht="15.75" customHeight="1"/>
-    <row r="116" ht="15.75" customHeight="1"/>
-    <row r="117" ht="15.75" customHeight="1"/>
-    <row r="118" ht="15.75" customHeight="1"/>
-    <row r="119" ht="15.75" customHeight="1"/>
-    <row r="120" ht="15.75" customHeight="1"/>
-    <row r="121" ht="15.75" customHeight="1"/>
-    <row r="122" ht="15.75" customHeight="1"/>
-    <row r="123" ht="15.75" customHeight="1"/>
-    <row r="124" ht="15.75" customHeight="1"/>
-    <row r="125" ht="15.75" customHeight="1"/>
-    <row r="126" ht="15.75" customHeight="1"/>
-    <row r="127" ht="15.75" customHeight="1"/>
-    <row r="128" ht="15.75" customHeight="1"/>
-    <row r="129" ht="15.75" customHeight="1"/>
-    <row r="130" ht="15.75" customHeight="1"/>
-    <row r="131" ht="15.75" customHeight="1"/>
-    <row r="132" ht="15.75" customHeight="1"/>
-    <row r="133" ht="15.75" customHeight="1"/>
-    <row r="134" ht="15.75" customHeight="1"/>
-    <row r="135" ht="15.75" customHeight="1"/>
-    <row r="136" ht="15.75" customHeight="1"/>
-    <row r="137" ht="15.75" customHeight="1"/>
-    <row r="138" ht="15.75" customHeight="1"/>
-    <row r="139" ht="15.75" customHeight="1"/>
-    <row r="140" ht="15.75" customHeight="1"/>
-    <row r="141" ht="15.75" customHeight="1"/>
-    <row r="142" ht="15.75" customHeight="1"/>
-    <row r="143" ht="15.75" customHeight="1"/>
-    <row r="144" ht="15.75" customHeight="1"/>
-    <row r="145" ht="15.75" customHeight="1"/>
-    <row r="146" ht="15.75" customHeight="1"/>
-    <row r="147" ht="15.75" customHeight="1"/>
-    <row r="148" ht="15.75" customHeight="1"/>
-    <row r="149" ht="15.75" customHeight="1"/>
-    <row r="150" ht="15.75" customHeight="1"/>
-    <row r="151" ht="15.75" customHeight="1"/>
-    <row r="152" ht="15.75" customHeight="1"/>
-    <row r="153" ht="15.75" customHeight="1"/>
-    <row r="154" ht="15.75" customHeight="1"/>
-    <row r="155" ht="15.75" customHeight="1"/>
-    <row r="156" ht="15.75" customHeight="1"/>
-    <row r="157" ht="15.75" customHeight="1"/>
-    <row r="158" ht="15.75" customHeight="1"/>
-    <row r="159" ht="15.75" customHeight="1"/>
-    <row r="160" ht="15.75" customHeight="1"/>
-    <row r="161" ht="15.75" customHeight="1"/>
-    <row r="162" ht="15.75" customHeight="1"/>
-    <row r="163" ht="15.75" customHeight="1"/>
-    <row r="164" ht="15.75" customHeight="1"/>
-    <row r="165" ht="15.75" customHeight="1"/>
-    <row r="166" ht="15.75" customHeight="1"/>
-    <row r="167" ht="15.75" customHeight="1"/>
-    <row r="168" ht="15.75" customHeight="1"/>
-    <row r="169" ht="15.75" customHeight="1"/>
-    <row r="170" ht="15.75" customHeight="1"/>
-    <row r="171" ht="15.75" customHeight="1"/>
-    <row r="172" ht="15.75" customHeight="1"/>
-    <row r="173" ht="15.75" customHeight="1"/>
-    <row r="174" ht="15.75" customHeight="1"/>
-    <row r="175" ht="15.75" customHeight="1"/>
-    <row r="176" ht="15.75" customHeight="1"/>
-    <row r="177" ht="15.75" customHeight="1"/>
-    <row r="178" ht="15.75" customHeight="1"/>
-    <row r="179" ht="15.75" customHeight="1"/>
-    <row r="180" ht="15.75" customHeight="1"/>
-    <row r="181" ht="15.75" customHeight="1"/>
-    <row r="182" ht="15.75" customHeight="1"/>
-    <row r="183" ht="15.75" customHeight="1"/>
-    <row r="184" ht="15.75" customHeight="1"/>
-    <row r="185" ht="15.75" customHeight="1"/>
-    <row r="186" ht="15.75" customHeight="1"/>
-    <row r="187" ht="15.75" customHeight="1"/>
-    <row r="188" ht="15.75" customHeight="1"/>
-    <row r="189" ht="15.75" customHeight="1"/>
-    <row r="190" ht="15.75" customHeight="1"/>
-    <row r="191" ht="15.75" customHeight="1"/>
-    <row r="192" ht="15.75" customHeight="1"/>
-    <row r="193" ht="15.75" customHeight="1"/>
-    <row r="194" ht="15.75" customHeight="1"/>
-    <row r="195" ht="15.75" customHeight="1"/>
-    <row r="196" ht="15.75" customHeight="1"/>
-    <row r="197" ht="15.75" customHeight="1"/>
-    <row r="198" ht="15.75" customHeight="1"/>
-    <row r="199" ht="15.75" customHeight="1"/>
-    <row r="200" ht="15.75" customHeight="1"/>
-    <row r="201" ht="15.75" customHeight="1"/>
-    <row r="202" ht="15.75" customHeight="1"/>
-    <row r="203" ht="15.75" customHeight="1"/>
-    <row r="204" ht="15.75" customHeight="1"/>
-    <row r="205" ht="15.75" customHeight="1"/>
-    <row r="206" ht="15.75" customHeight="1"/>
-    <row r="207" ht="15.75" customHeight="1"/>
-    <row r="208" ht="15.75" customHeight="1"/>
-    <row r="209" ht="15.75" customHeight="1"/>
-    <row r="210" ht="15.75" customHeight="1"/>
-    <row r="211" ht="15.75" customHeight="1"/>
-    <row r="212" ht="15.75" customHeight="1"/>
-    <row r="213" ht="15.75" customHeight="1"/>
-    <row r="214" ht="15.75" customHeight="1"/>
-    <row r="215" ht="15.75" customHeight="1"/>
-    <row r="216" ht="15.75" customHeight="1"/>
-    <row r="217" ht="15.75" customHeight="1"/>
-    <row r="218" ht="15.75" customHeight="1"/>
-    <row r="219" ht="15.75" customHeight="1"/>
-    <row r="220" ht="15.75" customHeight="1"/>
-    <row r="221" ht="15.75" customHeight="1"/>
-    <row r="222" ht="15.75" customHeight="1"/>
-    <row r="223" ht="15.75" customHeight="1"/>
-    <row r="224" ht="15.75" customHeight="1"/>
-    <row r="225" ht="15.75" customHeight="1"/>
-    <row r="226" ht="15.75" customHeight="1"/>
-    <row r="227" ht="15.75" customHeight="1"/>
-    <row r="228" ht="15.75" customHeight="1"/>
-    <row r="229" ht="15.75" customHeight="1"/>
-    <row r="230" ht="15.75" customHeight="1"/>
-    <row r="231" ht="15.75" customHeight="1"/>
-    <row r="232" ht="15.75" customHeight="1"/>
-    <row r="233" ht="15.75" customHeight="1"/>
-    <row r="234" ht="15.75" customHeight="1"/>
-    <row r="235" ht="15.75" customHeight="1"/>
-    <row r="236" ht="15.75" customHeight="1"/>
-    <row r="237" ht="15.75" customHeight="1"/>
-    <row r="238" ht="15.75" customHeight="1"/>
-    <row r="239" ht="15.75" customHeight="1"/>
-    <row r="240" ht="15.75" customHeight="1"/>
-    <row r="241" ht="15.75" customHeight="1"/>
-    <row r="242" ht="15.75" customHeight="1"/>
-    <row r="243" ht="15.75" customHeight="1"/>
-    <row r="244" ht="15.75" customHeight="1"/>
-    <row r="245" ht="15.75" customHeight="1"/>
-    <row r="246" ht="15.75" customHeight="1"/>
-    <row r="247" ht="15.75" customHeight="1"/>
-    <row r="248" ht="15.75" customHeight="1"/>
-    <row r="249" ht="15.75" customHeight="1"/>
-    <row r="250" ht="15.75" customHeight="1"/>
-    <row r="251" ht="15.75" customHeight="1"/>
-    <row r="252" ht="15.75" customHeight="1"/>
-    <row r="253" ht="15.75" customHeight="1"/>
-    <row r="254" ht="15.75" customHeight="1"/>
-    <row r="255" ht="15.75" customHeight="1"/>
-    <row r="256" ht="15.75" customHeight="1"/>
-    <row r="257" ht="15.75" customHeight="1"/>
-    <row r="258" ht="15.75" customHeight="1"/>
-    <row r="259" ht="15.75" customHeight="1"/>
-    <row r="260" ht="15.75" customHeight="1"/>
-    <row r="261" ht="15.75" customHeight="1"/>
-    <row r="262" ht="15.75" customHeight="1"/>
-    <row r="263" ht="15.75" customHeight="1"/>
-    <row r="264" ht="15.75" customHeight="1"/>
-    <row r="265" ht="15.75" customHeight="1"/>
-    <row r="266" ht="15.75" customHeight="1"/>
-    <row r="267" ht="15.75" customHeight="1"/>
-    <row r="268" ht="15.75" customHeight="1"/>
-    <row r="269" ht="15.75" customHeight="1"/>
-    <row r="270" ht="15.75" customHeight="1"/>
-    <row r="271" ht="15.75" customHeight="1"/>
-    <row r="272" ht="15.75" customHeight="1"/>
-    <row r="273" ht="15.75" customHeight="1"/>
-    <row r="274" ht="15.75" customHeight="1"/>
-    <row r="275" ht="15.75" customHeight="1"/>
-    <row r="276" ht="15.75" customHeight="1"/>
-    <row r="277" ht="15.75" customHeight="1"/>
-    <row r="278" ht="15.75" customHeight="1"/>
-    <row r="279" ht="15.75" customHeight="1"/>
-    <row r="280" ht="15.75" customHeight="1"/>
-    <row r="281" ht="15.75" customHeight="1"/>
-    <row r="282" ht="15.75" customHeight="1"/>
-    <row r="283" ht="15.75" customHeight="1"/>
-    <row r="284" ht="15.75" customHeight="1"/>
-    <row r="285" ht="15.75" customHeight="1"/>
-    <row r="286" ht="15.75" customHeight="1"/>
-    <row r="287" ht="15.75" customHeight="1"/>
-    <row r="288" ht="15.75" customHeight="1"/>
-    <row r="289" ht="15.75" customHeight="1"/>
-    <row r="290" ht="15.75" customHeight="1"/>
-    <row r="291" ht="15.75" customHeight="1"/>
-    <row r="292" ht="15.75" customHeight="1"/>
-    <row r="293" ht="15.75" customHeight="1"/>
-    <row r="294" ht="15.75" customHeight="1"/>
-    <row r="295" ht="15.75" customHeight="1"/>
-    <row r="296" ht="15.75" customHeight="1"/>
-    <row r="297" ht="15.75" customHeight="1"/>
-    <row r="298" ht="15.75" customHeight="1"/>
-    <row r="299" ht="15.75" customHeight="1"/>
-    <row r="300" ht="15.75" customHeight="1"/>
-    <row r="301" ht="15.75" customHeight="1"/>
-    <row r="302" ht="15.75" customHeight="1"/>
-    <row r="303" ht="15.75" customHeight="1"/>
-    <row r="304" ht="15.75" customHeight="1"/>
-    <row r="305" ht="15.75" customHeight="1"/>
-    <row r="306" ht="15.75" customHeight="1"/>
-    <row r="307" ht="15.75" customHeight="1"/>
-    <row r="308" ht="15.75" customHeight="1"/>
-    <row r="309" ht="15.75" customHeight="1"/>
-    <row r="310" ht="15.75" customHeight="1"/>
-    <row r="311" ht="15.75" customHeight="1"/>
-    <row r="312" ht="15.75" customHeight="1"/>
-    <row r="313" ht="15.75" customHeight="1"/>
-    <row r="314" ht="15.75" customHeight="1"/>
-    <row r="315" ht="15.75" customHeight="1"/>
-    <row r="316" ht="15.75" customHeight="1"/>
-    <row r="317" ht="15.75" customHeight="1"/>
-    <row r="318" ht="15.75" customHeight="1"/>
-    <row r="319" ht="15.75" customHeight="1"/>
-    <row r="320" ht="15.75" customHeight="1"/>
-    <row r="321" ht="15.75" customHeight="1"/>
-    <row r="322" ht="15.75" customHeight="1"/>
-    <row r="323" ht="15.75" customHeight="1"/>
-    <row r="324" ht="15.75" customHeight="1"/>
-    <row r="325" ht="15.75" customHeight="1"/>
-    <row r="326" ht="15.75" customHeight="1"/>
-    <row r="327" ht="15.75" customHeight="1"/>
-    <row r="328" ht="15.75" customHeight="1"/>
-    <row r="329" ht="15.75" customHeight="1"/>
-    <row r="330" ht="15.75" customHeight="1"/>
-    <row r="331" ht="15.75" customHeight="1"/>
-    <row r="332" ht="15.75" customHeight="1"/>
-    <row r="333" ht="15.75" customHeight="1"/>
-    <row r="334" ht="15.75" customHeight="1"/>
-    <row r="335" ht="15.75" customHeight="1"/>
-    <row r="336" ht="15.75" customHeight="1"/>
-    <row r="337" ht="15.75" customHeight="1"/>
-    <row r="338" ht="15.75" customHeight="1"/>
-    <row r="339" ht="15.75" customHeight="1"/>
-    <row r="340" ht="15.75" customHeight="1"/>
-    <row r="341" ht="15.75" customHeight="1"/>
-    <row r="342" ht="15.75" customHeight="1"/>
-    <row r="343" ht="15.75" customHeight="1"/>
-    <row r="344" ht="15.75" customHeight="1"/>
-    <row r="345" ht="15.75" customHeight="1"/>
-    <row r="346" ht="15.75" customHeight="1"/>
-    <row r="347" ht="15.75" customHeight="1"/>
-    <row r="348" ht="15.75" customHeight="1"/>
-    <row r="349" ht="15.75" customHeight="1"/>
-    <row r="350" ht="15.75" customHeight="1"/>
-    <row r="351" ht="15.75" customHeight="1"/>
-    <row r="352" ht="15.75" customHeight="1"/>
-    <row r="353" ht="15.75" customHeight="1"/>
-    <row r="354" ht="15.75" customHeight="1"/>
-    <row r="355" ht="15.75" customHeight="1"/>
-    <row r="356" ht="15.75" customHeight="1"/>
-    <row r="357" ht="15.75" customHeight="1"/>
-    <row r="358" ht="15.75" customHeight="1"/>
-    <row r="359" ht="15.75" customHeight="1"/>
-    <row r="360" ht="15.75" customHeight="1"/>
-    <row r="361" ht="15.75" customHeight="1"/>
-    <row r="362" ht="15.75" customHeight="1"/>
-    <row r="363" ht="15.75" customHeight="1"/>
-    <row r="364" ht="15.75" customHeight="1"/>
-    <row r="365" ht="15.75" customHeight="1"/>
-    <row r="366" ht="15.75" customHeight="1"/>
-    <row r="367" ht="15.75" customHeight="1"/>
-    <row r="368" ht="15.75" customHeight="1"/>
-    <row r="369" ht="15.75" customHeight="1"/>
-    <row r="370" ht="15.75" customHeight="1"/>
-    <row r="371" ht="15.75" customHeight="1"/>
-    <row r="372" ht="15.75" customHeight="1"/>
-    <row r="373" ht="15.75" customHeight="1"/>
-    <row r="374" ht="15.75" customHeight="1"/>
-    <row r="375" ht="15.75" customHeight="1"/>
-    <row r="376" ht="15.75" customHeight="1"/>
-    <row r="377" ht="15.75" customHeight="1"/>
-    <row r="378" ht="15.75" customHeight="1"/>
-    <row r="379" ht="15.75" customHeight="1"/>
-    <row r="380" ht="15.75" customHeight="1"/>
-    <row r="381" ht="15.75" customHeight="1"/>
-    <row r="382" ht="15.75" customHeight="1"/>
-    <row r="383" ht="15.75" customHeight="1"/>
-    <row r="384" ht="15.75" customHeight="1"/>
-    <row r="385" ht="15.75" customHeight="1"/>
-    <row r="386" ht="15.75" customHeight="1"/>
-    <row r="387" ht="15.75" customHeight="1"/>
-    <row r="388" ht="15.75" customHeight="1"/>
-    <row r="389" ht="15.75" customHeight="1"/>
-    <row r="390" ht="15.75" customHeight="1"/>
-    <row r="391" ht="15.75" customHeight="1"/>
-    <row r="392" ht="15.75" customHeight="1"/>
-    <row r="393" ht="15.75" customHeight="1"/>
-    <row r="394" ht="15.75" customHeight="1"/>
-    <row r="395" ht="15.75" customHeight="1"/>
-    <row r="396" ht="15.75" customHeight="1"/>
-    <row r="397" ht="15.75" customHeight="1"/>
-    <row r="398" ht="15.75" customHeight="1"/>
-    <row r="399" ht="15.75" customHeight="1"/>
-    <row r="400" ht="15.75" customHeight="1"/>
-    <row r="401" ht="15.75" customHeight="1"/>
-    <row r="402" ht="15.75" customHeight="1"/>
-    <row r="403" ht="15.75" customHeight="1"/>
-    <row r="404" ht="15.75" customHeight="1"/>
-    <row r="405" ht="15.75" customHeight="1"/>
-    <row r="406" ht="15.75" customHeight="1"/>
-    <row r="407" ht="15.75" customHeight="1"/>
-    <row r="408" ht="15.75" customHeight="1"/>
-    <row r="409" ht="15.75" customHeight="1"/>
-    <row r="410" ht="15.75" customHeight="1"/>
-    <row r="411" ht="15.75" customHeight="1"/>
-    <row r="412" ht="15.75" customHeight="1"/>
-    <row r="413" ht="15.75" customHeight="1"/>
-    <row r="414" ht="15.75" customHeight="1"/>
-    <row r="415" ht="15.75" customHeight="1"/>
-    <row r="416" ht="15.75" customHeight="1"/>
-    <row r="417" ht="15.75" customHeight="1"/>
-    <row r="418" ht="15.75" customHeight="1"/>
-    <row r="419" ht="15.75" customHeight="1"/>
-    <row r="420" ht="15.75" customHeight="1"/>
-    <row r="421" ht="15.75" customHeight="1"/>
-    <row r="422" ht="15.75" customHeight="1"/>
-    <row r="423" ht="15.75" customHeight="1"/>
-    <row r="424" ht="15.75" customHeight="1"/>
-    <row r="425" ht="15.75" customHeight="1"/>
-    <row r="426" ht="15.75" customHeight="1"/>
-    <row r="427" ht="15.75" customHeight="1"/>
-    <row r="428" ht="15.75" customHeight="1"/>
-    <row r="429" ht="15.75" customHeight="1"/>
-    <row r="430" ht="15.75" customHeight="1"/>
-    <row r="431" ht="15.75" customHeight="1"/>
-    <row r="432" ht="15.75" customHeight="1"/>
-    <row r="433" ht="15.75" customHeight="1"/>
-    <row r="434" ht="15.75" customHeight="1"/>
-    <row r="435" ht="15.75" customHeight="1"/>
-    <row r="436" ht="15.75" customHeight="1"/>
-    <row r="437" ht="15.75" customHeight="1"/>
-    <row r="438" ht="15.75" customHeight="1"/>
-    <row r="439" ht="15.75" customHeight="1"/>
-    <row r="440" ht="15.75" customHeight="1"/>
-    <row r="441" ht="15.75" customHeight="1"/>
-    <row r="442" ht="15.75" customHeight="1"/>
-    <row r="443" ht="15.75" customHeight="1"/>
-    <row r="444" ht="15.75" customHeight="1"/>
-    <row r="445" ht="15.75" customHeight="1"/>
-    <row r="446" ht="15.75" customHeight="1"/>
-    <row r="447" ht="15.75" customHeight="1"/>
-    <row r="448" ht="15.75" customHeight="1"/>
-    <row r="449" ht="15.75" customHeight="1"/>
-    <row r="450" ht="15.75" customHeight="1"/>
-    <row r="451" ht="15.75" customHeight="1"/>
-    <row r="452" ht="15.75" customHeight="1"/>
-    <row r="453" ht="15.75" customHeight="1"/>
-    <row r="454" ht="15.75" customHeight="1"/>
-    <row r="455" ht="15.75" customHeight="1"/>
-    <row r="456" ht="15.75" customHeight="1"/>
-    <row r="457" ht="15.75" customHeight="1"/>
-    <row r="458" ht="15.75" customHeight="1"/>
-    <row r="459" ht="15.75" customHeight="1"/>
-    <row r="460" ht="15.75" customHeight="1"/>
-    <row r="461" ht="15.75" customHeight="1"/>
-    <row r="462" ht="15.75" customHeight="1"/>
-    <row r="463" ht="15.75" customHeight="1"/>
-    <row r="464" ht="15.75" customHeight="1"/>
-    <row r="465" ht="15.75" customHeight="1"/>
-    <row r="466" ht="15.75" customHeight="1"/>
-    <row r="467" ht="15.75" customHeight="1"/>
-    <row r="468" ht="15.75" customHeight="1"/>
-    <row r="469" ht="15.75" customHeight="1"/>
-    <row r="470" ht="15.75" customHeight="1"/>
-    <row r="471" ht="15.75" customHeight="1"/>
-    <row r="472" ht="15.75" customHeight="1"/>
-    <row r="473" ht="15.75" customHeight="1"/>
-    <row r="474" ht="15.75" customHeight="1"/>
-    <row r="475" ht="15.75" customHeight="1"/>
-    <row r="476" ht="15.75" customHeight="1"/>
-    <row r="477" ht="15.75" customHeight="1"/>
-    <row r="478" ht="15.75" customHeight="1"/>
-    <row r="479" ht="15.75" customHeight="1"/>
-    <row r="480" ht="15.75" customHeight="1"/>
-    <row r="481" ht="15.75" customHeight="1"/>
-    <row r="482" ht="15.75" customHeight="1"/>
-    <row r="483" ht="15.75" customHeight="1"/>
-    <row r="484" ht="15.75" customHeight="1"/>
-    <row r="485" ht="15.75" customHeight="1"/>
-    <row r="486" ht="15.75" customHeight="1"/>
-    <row r="487" ht="15.75" customHeight="1"/>
-    <row r="488" ht="15.75" customHeight="1"/>
-    <row r="489" ht="15.75" customHeight="1"/>
-    <row r="490" ht="15.75" customHeight="1"/>
-    <row r="491" ht="15.75" customHeight="1"/>
-    <row r="492" ht="15.75" customHeight="1"/>
-    <row r="493" ht="15.75" customHeight="1"/>
-    <row r="494" ht="15.75" customHeight="1"/>
-    <row r="495" ht="15.75" customHeight="1"/>
-    <row r="496" ht="15.75" customHeight="1"/>
-    <row r="497" ht="15.75" customHeight="1"/>
-    <row r="498" ht="15.75" customHeight="1"/>
-    <row r="499" ht="15.75" customHeight="1"/>
-    <row r="500" ht="15.75" customHeight="1"/>
-    <row r="501" ht="15.75" customHeight="1"/>
-    <row r="502" ht="15.75" customHeight="1"/>
-    <row r="503" ht="15.75" customHeight="1"/>
-    <row r="504" ht="15.75" customHeight="1"/>
-    <row r="505" ht="15.75" customHeight="1"/>
-    <row r="506" ht="15.75" customHeight="1"/>
-    <row r="507" ht="15.75" customHeight="1"/>
-    <row r="508" ht="15.75" customHeight="1"/>
-    <row r="509" ht="15.75" customHeight="1"/>
-    <row r="510" ht="15.75" customHeight="1"/>
-    <row r="511" ht="15.75" customHeight="1"/>
-    <row r="512" ht="15.75" customHeight="1"/>
-    <row r="513" ht="15.75" customHeight="1"/>
-    <row r="514" ht="15.75" customHeight="1"/>
-    <row r="515" ht="15.75" customHeight="1"/>
-    <row r="516" ht="15.75" customHeight="1"/>
-    <row r="517" ht="15.75" customHeight="1"/>
-    <row r="518" ht="15.75" customHeight="1"/>
-    <row r="519" ht="15.75" customHeight="1"/>
-    <row r="520" ht="15.75" customHeight="1"/>
-    <row r="521" ht="15.75" customHeight="1"/>
-    <row r="522" ht="15.75" customHeight="1"/>
-    <row r="523" ht="15.75" customHeight="1"/>
-    <row r="524" ht="15.75" customHeight="1"/>
-    <row r="525" ht="15.75" customHeight="1"/>
-    <row r="526" ht="15.75" customHeight="1"/>
-    <row r="527" ht="15.75" customHeight="1"/>
-    <row r="528" ht="15.75" customHeight="1"/>
-    <row r="529" ht="15.75" customHeight="1"/>
-    <row r="530" ht="15.75" customHeight="1"/>
-    <row r="531" ht="15.75" customHeight="1"/>
-    <row r="532" ht="15.75" customHeight="1"/>
-    <row r="533" ht="15.75" customHeight="1"/>
-    <row r="534" ht="15.75" customHeight="1"/>
-    <row r="535" ht="15.75" customHeight="1"/>
-    <row r="536" ht="15.75" customHeight="1"/>
-    <row r="537" ht="15.75" customHeight="1"/>
-    <row r="538" ht="15.75" customHeight="1"/>
-    <row r="539" ht="15.75" customHeight="1"/>
-    <row r="540" ht="15.75" customHeight="1"/>
-    <row r="541" ht="15.75" customHeight="1"/>
-    <row r="542" ht="15.75" customHeight="1"/>
-    <row r="543" ht="15.75" customHeight="1"/>
-    <row r="544" ht="15.75" customHeight="1"/>
-    <row r="545" ht="15.75" customHeight="1"/>
-    <row r="546" ht="15.75" customHeight="1"/>
-    <row r="547" ht="15.75" customHeight="1"/>
-    <row r="548" ht="15.75" customHeight="1"/>
-    <row r="549" ht="15.75" customHeight="1"/>
-    <row r="550" ht="15.75" customHeight="1"/>
-    <row r="551" ht="15.75" customHeight="1"/>
-    <row r="552" ht="15.75" customHeight="1"/>
-    <row r="553" ht="15.75" customHeight="1"/>
-    <row r="554" ht="15.75" customHeight="1"/>
-    <row r="555" ht="15.75" customHeight="1"/>
-    <row r="556" ht="15.75" customHeight="1"/>
-    <row r="557" ht="15.75" customHeight="1"/>
-    <row r="558" ht="15.75" customHeight="1"/>
-    <row r="559" ht="15.75" customHeight="1"/>
-    <row r="560" ht="15.75" customHeight="1"/>
-    <row r="561" ht="15.75" customHeight="1"/>
-    <row r="562" ht="15.75" customHeight="1"/>
-    <row r="563" ht="15.75" customHeight="1"/>
-    <row r="564" ht="15.75" customHeight="1"/>
-    <row r="565" ht="15.75" customHeight="1"/>
-    <row r="566" ht="15.75" customHeight="1"/>
-    <row r="567" ht="15.75" customHeight="1"/>
-    <row r="568" ht="15.75" customHeight="1"/>
-    <row r="569" ht="15.75" customHeight="1"/>
-    <row r="570" ht="15.75" customHeight="1"/>
-    <row r="571" ht="15.75" customHeight="1"/>
-    <row r="572" ht="15.75" customHeight="1"/>
-    <row r="573" ht="15.75" customHeight="1"/>
-    <row r="574" ht="15.75" customHeight="1"/>
-    <row r="575" ht="15.75" customHeight="1"/>
-    <row r="576" ht="15.75" customHeight="1"/>
-    <row r="577" ht="15.75" customHeight="1"/>
-    <row r="578" ht="15.75" customHeight="1"/>
-    <row r="579" ht="15.75" customHeight="1"/>
-    <row r="580" ht="15.75" customHeight="1"/>
-    <row r="581" ht="15.75" customHeight="1"/>
-    <row r="582" ht="15.75" customHeight="1"/>
-    <row r="583" ht="15.75" customHeight="1"/>
-    <row r="584" ht="15.75" customHeight="1"/>
-    <row r="585" ht="15.75" customHeight="1"/>
-    <row r="586" ht="15.75" customHeight="1"/>
-    <row r="587" ht="15.75" customHeight="1"/>
-    <row r="588" ht="15.75" customHeight="1"/>
-    <row r="589" ht="15.75" customHeight="1"/>
-    <row r="590" ht="15.75" customHeight="1"/>
-    <row r="591" ht="15.75" customHeight="1"/>
-    <row r="592" ht="15.75" customHeight="1"/>
-    <row r="593" ht="15.75" customHeight="1"/>
-    <row r="594" ht="15.75" customHeight="1"/>
-    <row r="595" ht="15.75" customHeight="1"/>
-    <row r="596" ht="15.75" customHeight="1"/>
-    <row r="597" ht="15.75" customHeight="1"/>
-    <row r="598" ht="15.75" customHeight="1"/>
-    <row r="599" ht="15.75" customHeight="1"/>
-    <row r="600" ht="15.75" customHeight="1"/>
-    <row r="601" ht="15.75" customHeight="1"/>
-    <row r="602" ht="15.75" customHeight="1"/>
-    <row r="603" ht="15.75" customHeight="1"/>
-    <row r="604" ht="15.75" customHeight="1"/>
-    <row r="605" ht="15.75" customHeight="1"/>
-    <row r="606" ht="15.75" customHeight="1"/>
-    <row r="607" ht="15.75" customHeight="1"/>
-    <row r="608" ht="15.75" customHeight="1"/>
-    <row r="609" ht="15.75" customHeight="1"/>
-    <row r="610" ht="15.75" customHeight="1"/>
-    <row r="611" ht="15.75" customHeight="1"/>
-    <row r="612" ht="15.75" customHeight="1"/>
-    <row r="613" ht="15.75" customHeight="1"/>
-    <row r="614" ht="15.75" customHeight="1"/>
-    <row r="615" ht="15.75" customHeight="1"/>
-    <row r="616" ht="15.75" customHeight="1"/>
-    <row r="617" ht="15.75" customHeight="1"/>
-    <row r="618" ht="15.75" customHeight="1"/>
-    <row r="619" ht="15.75" customHeight="1"/>
-    <row r="620" ht="15.75" customHeight="1"/>
-    <row r="621" ht="15.75" customHeight="1"/>
-    <row r="622" ht="15.75" customHeight="1"/>
-    <row r="623" ht="15.75" customHeight="1"/>
-    <row r="624" ht="15.75" customHeight="1"/>
-    <row r="625" ht="15.75" customHeight="1"/>
-    <row r="626" ht="15.75" customHeight="1"/>
-    <row r="627" ht="15.75" customHeight="1"/>
-    <row r="628" ht="15.75" customHeight="1"/>
-    <row r="629" ht="15.75" customHeight="1"/>
-    <row r="630" ht="15.75" customHeight="1"/>
-    <row r="631" ht="15.75" customHeight="1"/>
-    <row r="632" ht="15.75" customHeight="1"/>
-    <row r="633" ht="15.75" customHeight="1"/>
-    <row r="634" ht="15.75" customHeight="1"/>
-    <row r="635" ht="15.75" customHeight="1"/>
-    <row r="636" ht="15.75" customHeight="1"/>
-    <row r="637" ht="15.75" customHeight="1"/>
-    <row r="638" ht="15.75" customHeight="1"/>
-    <row r="639" ht="15.75" customHeight="1"/>
-    <row r="640" ht="15.75" customHeight="1"/>
-    <row r="641" ht="15.75" customHeight="1"/>
-    <row r="642" ht="15.75" customHeight="1"/>
-    <row r="643" ht="15.75" customHeight="1"/>
-    <row r="644" ht="15.75" customHeight="1"/>
-    <row r="645" ht="15.75" customHeight="1"/>
-    <row r="646" ht="15.75" customHeight="1"/>
-    <row r="647" ht="15.75" customHeight="1"/>
-    <row r="648" ht="15.75" customHeight="1"/>
-    <row r="649" ht="15.75" customHeight="1"/>
-    <row r="650" ht="15.75" customHeight="1"/>
-    <row r="651" ht="15.75" customHeight="1"/>
-    <row r="652" ht="15.75" customHeight="1"/>
-    <row r="653" ht="15.75" customHeight="1"/>
-    <row r="654" ht="15.75" customHeight="1"/>
-    <row r="655" ht="15.75" customHeight="1"/>
-    <row r="656" ht="15.75" customHeight="1"/>
-    <row r="657" ht="15.75" customHeight="1"/>
-    <row r="658" ht="15.75" customHeight="1"/>
-    <row r="659" ht="15.75" customHeight="1"/>
-    <row r="660" ht="15.75" customHeight="1"/>
-    <row r="661" ht="15.75" customHeight="1"/>
-    <row r="662" ht="15.75" customHeight="1"/>
-    <row r="663" ht="15.75" customHeight="1"/>
-    <row r="664" ht="15.75" customHeight="1"/>
-    <row r="665" ht="15.75" customHeight="1"/>
-    <row r="666" ht="15.75" customHeight="1"/>
-    <row r="667" ht="15.75" customHeight="1"/>
-    <row r="668" ht="15.75" customHeight="1"/>
-    <row r="669" ht="15.75" customHeight="1"/>
-    <row r="670" ht="15.75" customHeight="1"/>
-    <row r="671" ht="15.75" customHeight="1"/>
-    <row r="672" ht="15.75" customHeight="1"/>
-    <row r="673" ht="15.75" customHeight="1"/>
-    <row r="674" ht="15.75" customHeight="1"/>
-    <row r="675" ht="15.75" customHeight="1"/>
-    <row r="676" ht="15.75" customHeight="1"/>
-    <row r="677" ht="15.75" customHeight="1"/>
-    <row r="678" ht="15.75" customHeight="1"/>
-    <row r="679" ht="15.75" customHeight="1"/>
-    <row r="680" ht="15.75" customHeight="1"/>
-    <row r="681" ht="15.75" customHeight="1"/>
-    <row r="682" ht="15.75" customHeight="1"/>
-    <row r="683" ht="15.75" customHeight="1"/>
-    <row r="684" ht="15.75" customHeight="1"/>
-    <row r="685" ht="15.75" customHeight="1"/>
-    <row r="686" ht="15.75" customHeight="1"/>
-    <row r="687" ht="15.75" customHeight="1"/>
-    <row r="688" ht="15.75" customHeight="1"/>
-    <row r="689" ht="15.75" customHeight="1"/>
-    <row r="690" ht="15.75" customHeight="1"/>
-    <row r="691" ht="15.75" customHeight="1"/>
-    <row r="692" ht="15.75" customHeight="1"/>
-    <row r="693" ht="15.75" customHeight="1"/>
-    <row r="694" ht="15.75" customHeight="1"/>
-    <row r="695" ht="15.75" customHeight="1"/>
-    <row r="696" ht="15.75" customHeight="1"/>
-    <row r="697" ht="15.75" customHeight="1"/>
-    <row r="698" ht="15.75" customHeight="1"/>
-    <row r="699" ht="15.75" customHeight="1"/>
-    <row r="700" ht="15.75" customHeight="1"/>
-    <row r="701" ht="15.75" customHeight="1"/>
-    <row r="702" ht="15.75" customHeight="1"/>
-    <row r="703" ht="15.75" customHeight="1"/>
-    <row r="704" ht="15.75" customHeight="1"/>
-    <row r="705" ht="15.75" customHeight="1"/>
-    <row r="706" ht="15.75" customHeight="1"/>
-    <row r="707" ht="15.75" customHeight="1"/>
-    <row r="708" ht="15.75" customHeight="1"/>
-    <row r="709" ht="15.75" customHeight="1"/>
-    <row r="710" ht="15.75" customHeight="1"/>
-    <row r="711" ht="15.75" customHeight="1"/>
-    <row r="712" ht="15.75" customHeight="1"/>
-    <row r="713" ht="15.75" customHeight="1"/>
-    <row r="714" ht="15.75" customHeight="1"/>
-    <row r="715" ht="15.75" customHeight="1"/>
-    <row r="716" ht="15.75" customHeight="1"/>
-    <row r="717" ht="15.75" customHeight="1"/>
-    <row r="718" ht="15.75" customHeight="1"/>
-    <row r="719" ht="15.75" customHeight="1"/>
-    <row r="720" ht="15.75" customHeight="1"/>
-    <row r="721" ht="15.75" customHeight="1"/>
-    <row r="722" ht="15.75" customHeight="1"/>
-    <row r="723" ht="15.75" customHeight="1"/>
-    <row r="724" ht="15.75" customHeight="1"/>
-    <row r="725" ht="15.75" customHeight="1"/>
-    <row r="726" ht="15.75" customHeight="1"/>
-    <row r="727" ht="15.75" customHeight="1"/>
-    <row r="728" ht="15.75" customHeight="1"/>
-    <row r="729" ht="15.75" customHeight="1"/>
-    <row r="730" ht="15.75" customHeight="1"/>
-    <row r="731" ht="15.75" customHeight="1"/>
-    <row r="732" ht="15.75" customHeight="1"/>
-    <row r="733" ht="15.75" customHeight="1"/>
-    <row r="734" ht="15.75" customHeight="1"/>
-    <row r="735" ht="15.75" customHeight="1"/>
-    <row r="736" ht="15.75" customHeight="1"/>
-    <row r="737" ht="15.75" customHeight="1"/>
-    <row r="738" ht="15.75" customHeight="1"/>
-    <row r="739" ht="15.75" customHeight="1"/>
-    <row r="740" ht="15.75" customHeight="1"/>
-    <row r="741" ht="15.75" customHeight="1"/>
-    <row r="742" ht="15.75" customHeight="1"/>
-    <row r="743" ht="15.75" customHeight="1"/>
-    <row r="744" ht="15.75" customHeight="1"/>
-    <row r="745" ht="15.75" customHeight="1"/>
-    <row r="746" ht="15.75" customHeight="1"/>
-    <row r="747" ht="15.75" customHeight="1"/>
-    <row r="748" ht="15.75" customHeight="1"/>
-    <row r="749" ht="15.75" customHeight="1"/>
-    <row r="750" ht="15.75" customHeight="1"/>
-    <row r="751" ht="15.75" customHeight="1"/>
-    <row r="752" ht="15.75" customHeight="1"/>
-    <row r="753" ht="15.75" customHeight="1"/>
-    <row r="754" ht="15.75" customHeight="1"/>
-    <row r="755" ht="15.75" customHeight="1"/>
-    <row r="756" ht="15.75" customHeight="1"/>
-    <row r="757" ht="15.75" customHeight="1"/>
-    <row r="758" ht="15.75" customHeight="1"/>
-    <row r="759" ht="15.75" customHeight="1"/>
-    <row r="760" ht="15.75" customHeight="1"/>
-    <row r="761" ht="15.75" customHeight="1"/>
-    <row r="762" ht="15.75" customHeight="1"/>
-    <row r="763" ht="15.75" customHeight="1"/>
-    <row r="764" ht="15.75" customHeight="1"/>
-    <row r="765" ht="15.75" customHeight="1"/>
-    <row r="766" ht="15.75" customHeight="1"/>
-    <row r="767" ht="15.75" customHeight="1"/>
-    <row r="768" ht="15.75" customHeight="1"/>
-    <row r="769" ht="15.75" customHeight="1"/>
-    <row r="770" ht="15.75" customHeight="1"/>
-    <row r="771" ht="15.75" customHeight="1"/>
-    <row r="772" ht="15.75" customHeight="1"/>
-    <row r="773" ht="15.75" customHeight="1"/>
-    <row r="774" ht="15.75" customHeight="1"/>
-    <row r="775" ht="15.75" customHeight="1"/>
-    <row r="776" ht="15.75" customHeight="1"/>
-    <row r="777" ht="15.75" customHeight="1"/>
-    <row r="778" ht="15.75" customHeight="1"/>
-    <row r="779" ht="15.75" customHeight="1"/>
-    <row r="780" ht="15.75" customHeight="1"/>
-    <row r="781" ht="15.75" customHeight="1"/>
-    <row r="782" ht="15.75" customHeight="1"/>
-    <row r="783" ht="15.75" customHeight="1"/>
-    <row r="784" ht="15.75" customHeight="1"/>
-    <row r="785" ht="15.75" customHeight="1"/>
-    <row r="786" ht="15.75" customHeight="1"/>
-    <row r="787" ht="15.75" customHeight="1"/>
-    <row r="788" ht="15.75" customHeight="1"/>
-    <row r="789" ht="15.75" customHeight="1"/>
-    <row r="790" ht="15.75" customHeight="1"/>
-    <row r="791" ht="15.75" customHeight="1"/>
-    <row r="792" ht="15.75" customHeight="1"/>
-    <row r="793" ht="15.75" customHeight="1"/>
-    <row r="794" ht="15.75" customHeight="1"/>
-    <row r="795" ht="15.75" customHeight="1"/>
-    <row r="796" ht="15.75" customHeight="1"/>
-    <row r="797" ht="15.75" customHeight="1"/>
-    <row r="798" ht="15.75" customHeight="1"/>
-    <row r="799" ht="15.75" customHeight="1"/>
-    <row r="800" ht="15.75" customHeight="1"/>
-    <row r="801" ht="15.75" customHeight="1"/>
-    <row r="802" ht="15.75" customHeight="1"/>
-    <row r="803" ht="15.75" customHeight="1"/>
-    <row r="804" ht="15.75" customHeight="1"/>
-    <row r="805" ht="15.75" customHeight="1"/>
-    <row r="806" ht="15.75" customHeight="1"/>
-    <row r="807" ht="15.75" customHeight="1"/>
-    <row r="808" ht="15.75" customHeight="1"/>
-    <row r="809" ht="15.75" customHeight="1"/>
-    <row r="810" ht="15.75" customHeight="1"/>
-    <row r="811" ht="15.75" customHeight="1"/>
-    <row r="812" ht="15.75" customHeight="1"/>
-    <row r="813" ht="15.75" customHeight="1"/>
-    <row r="814" ht="15.75" customHeight="1"/>
-    <row r="815" ht="15.75" customHeight="1"/>
-    <row r="816" ht="15.75" customHeight="1"/>
-    <row r="817" ht="15.75" customHeight="1"/>
-    <row r="818" ht="15.75" customHeight="1"/>
-    <row r="819" ht="15.75" customHeight="1"/>
-    <row r="820" ht="15.75" customHeight="1"/>
-    <row r="821" ht="15.75" customHeight="1"/>
-    <row r="822" ht="15.75" customHeight="1"/>
-    <row r="823" ht="15.75" customHeight="1"/>
-    <row r="824" ht="15.75" customHeight="1"/>
-    <row r="825" ht="15.75" customHeight="1"/>
-    <row r="826" ht="15.75" customHeight="1"/>
-    <row r="827" ht="15.75" customHeight="1"/>
-    <row r="828" ht="15.75" customHeight="1"/>
-    <row r="829" ht="15.75" customHeight="1"/>
-    <row r="830" ht="15.75" customHeight="1"/>
-    <row r="831" ht="15.75" customHeight="1"/>
-    <row r="832" ht="15.75" customHeight="1"/>
-    <row r="833" ht="15.75" customHeight="1"/>
-    <row r="834" ht="15.75" customHeight="1"/>
-    <row r="835" ht="15.75" customHeight="1"/>
-    <row r="836" ht="15.75" customHeight="1"/>
-    <row r="837" ht="15.75" customHeight="1"/>
-    <row r="838" ht="15.75" customHeight="1"/>
-    <row r="839" ht="15.75" customHeight="1"/>
-    <row r="840" ht="15.75" customHeight="1"/>
-    <row r="841" ht="15.75" customHeight="1"/>
-    <row r="842" ht="15.75" customHeight="1"/>
-    <row r="843" ht="15.75" customHeight="1"/>
-    <row r="844" ht="15.75" customHeight="1"/>
-    <row r="845" ht="15.75" customHeight="1"/>
-    <row r="846" ht="15.75" customHeight="1"/>
-    <row r="847" ht="15.75" customHeight="1"/>
-    <row r="848" ht="15.75" customHeight="1"/>
-    <row r="849" ht="15.75" customHeight="1"/>
-    <row r="850" ht="15.75" customHeight="1"/>
-    <row r="851" ht="15.75" customHeight="1"/>
-    <row r="852" ht="15.75" customHeight="1"/>
-    <row r="853" ht="15.75" customHeight="1"/>
-    <row r="854" ht="15.75" customHeight="1"/>
-    <row r="855" ht="15.75" customHeight="1"/>
-    <row r="856" ht="15.75" customHeight="1"/>
-    <row r="857" ht="15.75" customHeight="1"/>
-    <row r="858" ht="15.75" customHeight="1"/>
-    <row r="859" ht="15.75" customHeight="1"/>
-    <row r="860" ht="15.75" customHeight="1"/>
-    <row r="861" ht="15.75" customHeight="1"/>
-    <row r="862" ht="15.75" customHeight="1"/>
-    <row r="863" ht="15.75" customHeight="1"/>
-    <row r="864" ht="15.75" customHeight="1"/>
-    <row r="865" ht="15.75" customHeight="1"/>
-    <row r="866" ht="15.75" customHeight="1"/>
-    <row r="867" ht="15.75" customHeight="1"/>
-    <row r="868" ht="15.75" customHeight="1"/>
-    <row r="869" ht="15.75" customHeight="1"/>
-    <row r="870" ht="15.75" customHeight="1"/>
-    <row r="871" ht="15.75" customHeight="1"/>
-    <row r="872" ht="15.75" customHeight="1"/>
-    <row r="873" ht="15.75" customHeight="1"/>
-    <row r="874" ht="15.75" customHeight="1"/>
-    <row r="875" ht="15.75" customHeight="1"/>
-    <row r="876" ht="15.75" customHeight="1"/>
-    <row r="877" ht="15.75" customHeight="1"/>
-    <row r="878" ht="15.75" customHeight="1"/>
-    <row r="879" ht="15.75" customHeight="1"/>
-    <row r="880" ht="15.75" customHeight="1"/>
-    <row r="881" ht="15.75" customHeight="1"/>
-    <row r="882" ht="15.75" customHeight="1"/>
-    <row r="883" ht="15.75" customHeight="1"/>
-    <row r="884" ht="15.75" customHeight="1"/>
-    <row r="885" ht="15.75" customHeight="1"/>
-    <row r="886" ht="15.75" customHeight="1"/>
-    <row r="887" ht="15.75" customHeight="1"/>
-    <row r="888" ht="15.75" customHeight="1"/>
-    <row r="889" ht="15.75" customHeight="1"/>
-    <row r="890" ht="15.75" customHeight="1"/>
-    <row r="891" ht="15.75" customHeight="1"/>
-    <row r="892" ht="15.75" customHeight="1"/>
-    <row r="893" ht="15.75" customHeight="1"/>
-    <row r="894" ht="15.75" customHeight="1"/>
-    <row r="895" ht="15.75" customHeight="1"/>
-    <row r="896" ht="15.75" customHeight="1"/>
-    <row r="897" ht="15.75" customHeight="1"/>
-    <row r="898" ht="15.75" customHeight="1"/>
-    <row r="899" ht="15.75" customHeight="1"/>
-    <row r="900" ht="15.75" customHeight="1"/>
-    <row r="901" ht="15.75" customHeight="1"/>
-    <row r="902" ht="15.75" customHeight="1"/>
-    <row r="903" ht="15.75" customHeight="1"/>
-    <row r="904" ht="15.75" customHeight="1"/>
-    <row r="905" ht="15.75" customHeight="1"/>
-    <row r="906" ht="15.75" customHeight="1"/>
-    <row r="907" ht="15.75" customHeight="1"/>
-    <row r="908" ht="15.75" customHeight="1"/>
-    <row r="909" ht="15.75" customHeight="1"/>
-    <row r="910" ht="15.75" customHeight="1"/>
-    <row r="911" ht="15.75" customHeight="1"/>
-    <row r="912" ht="15.75" customHeight="1"/>
-    <row r="913" ht="15.75" customHeight="1"/>
-    <row r="914" ht="15.75" customHeight="1"/>
-    <row r="915" ht="15.75" customHeight="1"/>
-    <row r="916" ht="15.75" customHeight="1"/>
-    <row r="917" ht="15.75" customHeight="1"/>
-    <row r="918" ht="15.75" customHeight="1"/>
-    <row r="919" ht="15.75" customHeight="1"/>
-    <row r="920" ht="15.75" customHeight="1"/>
-    <row r="921" ht="15.75" customHeight="1"/>
-    <row r="922" ht="15.75" customHeight="1"/>
-    <row r="923" ht="15.75" customHeight="1"/>
-    <row r="924" ht="15.75" customHeight="1"/>
-    <row r="925" ht="15.75" customHeight="1"/>
-    <row r="926" ht="15.75" customHeight="1"/>
-    <row r="927" ht="15.75" customHeight="1"/>
-    <row r="928" ht="15.75" customHeight="1"/>
-    <row r="929" ht="15.75" customHeight="1"/>
-    <row r="930" ht="15.75" customHeight="1"/>
-    <row r="931" ht="15.75" customHeight="1"/>
-    <row r="932" ht="15.75" customHeight="1"/>
-    <row r="933" ht="15.75" customHeight="1"/>
-    <row r="934" ht="15.75" customHeight="1"/>
-    <row r="935" ht="15.75" customHeight="1"/>
-    <row r="936" ht="15.75" customHeight="1"/>
-    <row r="937" ht="15.75" customHeight="1"/>
-    <row r="938" ht="15.75" customHeight="1"/>
-    <row r="939" ht="15.75" customHeight="1"/>
-    <row r="940" ht="15.75" customHeight="1"/>
-    <row r="941" ht="15.75" customHeight="1"/>
-    <row r="942" ht="15.75" customHeight="1"/>
-    <row r="943" ht="15.75" customHeight="1"/>
-    <row r="944" ht="15.75" customHeight="1"/>
-    <row r="945" ht="15.75" customHeight="1"/>
-    <row r="946" ht="15.75" customHeight="1"/>
-    <row r="947" ht="15.75" customHeight="1"/>
-    <row r="948" ht="15.75" customHeight="1"/>
-    <row r="949" ht="15.75" customHeight="1"/>
-    <row r="950" ht="15.75" customHeight="1"/>
-    <row r="951" ht="15.75" customHeight="1"/>
-    <row r="952" ht="15.75" customHeight="1"/>
-    <row r="953" ht="15.75" customHeight="1"/>
-    <row r="954" ht="15.75" customHeight="1"/>
-    <row r="955" ht="15.75" customHeight="1"/>
-    <row r="956" ht="15.75" customHeight="1"/>
-    <row r="957" ht="15.75" customHeight="1"/>
-    <row r="958" ht="15.75" customHeight="1"/>
-    <row r="959" ht="15.75" customHeight="1"/>
-    <row r="960" ht="15.75" customHeight="1"/>
-    <row r="961" ht="15.75" customHeight="1"/>
-    <row r="962" ht="15.75" customHeight="1"/>
-    <row r="963" ht="15.75" customHeight="1"/>
-    <row r="964" ht="15.75" customHeight="1"/>
-    <row r="965" ht="15.75" customHeight="1"/>
-    <row r="966" ht="15.75" customHeight="1"/>
-    <row r="967" ht="15.75" customHeight="1"/>
-    <row r="968" ht="15.75" customHeight="1"/>
-    <row r="969" ht="15.75" customHeight="1"/>
-    <row r="970" ht="15.75" customHeight="1"/>
-    <row r="971" ht="15.75" customHeight="1"/>
-    <row r="972" ht="15.75" customHeight="1"/>
-    <row r="973" ht="15.75" customHeight="1"/>
-    <row r="974" ht="15.75" customHeight="1"/>
-    <row r="975" ht="15.75" customHeight="1"/>
-    <row r="976" ht="15.75" customHeight="1"/>
-    <row r="977" ht="15.75" customHeight="1"/>
-    <row r="978" ht="15.75" customHeight="1"/>
-    <row r="979" ht="15.75" customHeight="1"/>
-    <row r="980" ht="15.75" customHeight="1"/>
-    <row r="981" ht="15.75" customHeight="1"/>
-    <row r="982" ht="15.75" customHeight="1"/>
-    <row r="983" ht="15.75" customHeight="1"/>
-    <row r="984" ht="15.75" customHeight="1"/>
-    <row r="985" ht="15.75" customHeight="1"/>
-    <row r="986" ht="15.75" customHeight="1"/>
-    <row r="987" ht="15.75" customHeight="1"/>
-    <row r="988" ht="15.75" customHeight="1"/>
-    <row r="989" ht="15.75" customHeight="1"/>
-    <row r="990" ht="15.75" customHeight="1"/>
-    <row r="991" ht="15.75" customHeight="1"/>
-    <row r="992" ht="15.75" customHeight="1"/>
-    <row r="993" ht="15.75" customHeight="1"/>
-    <row r="994" ht="15.75" customHeight="1"/>
-    <row r="995" ht="15.75" customHeight="1"/>
-    <row r="996" ht="15.75" customHeight="1"/>
-    <row r="997" ht="15.75" customHeight="1"/>
-    <row r="998" ht="15.75" customHeight="1"/>
-    <row r="999" ht="15.75" customHeight="1"/>
-    <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="21" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="22" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="23" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="24" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="25" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="26" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="27" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="28" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="29" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="30" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="31" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="32" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="33" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="34" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="35" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="36" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="37" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="38" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="39" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="40" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="41" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="42" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="43" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="44" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="45" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="46" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="47" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="48" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="49" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="50" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="51" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="52" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="53" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="54" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="55" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="56" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="57" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="58" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="59" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="60" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="61" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="62" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="63" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="64" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="65" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="66" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="67" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="68" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="69" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="70" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="71" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="72" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="73" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="74" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="75" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="76" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="77" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="78" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="79" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="80" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="81" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="82" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="83" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="84" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="85" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="86" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="87" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="88" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="89" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="90" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="91" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="92" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="93" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="94" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="95" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="96" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="97" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="98" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="99" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="100" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="101" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="102" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="103" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="104" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="105" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="106" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="107" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="108" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="109" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="110" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="111" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="112" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="113" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="114" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="115" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="116" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="117" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="118" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="119" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="120" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="121" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="122" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="123" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="124" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="125" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="126" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="127" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="128" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="129" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="130" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="131" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="132" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="133" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="134" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="135" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="136" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="137" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="138" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="139" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="140" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="141" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="142" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="143" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="144" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="145" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="146" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="147" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="148" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="149" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="150" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="151" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="152" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="153" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="154" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="155" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="156" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="157" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="158" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="159" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="160" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="161" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="162" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="163" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="164" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="165" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="166" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="167" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="168" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="169" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="170" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="171" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="172" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="173" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="174" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="175" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="176" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="177" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="178" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="179" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="180" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="181" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="182" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="183" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="184" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="185" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="186" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="187" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="188" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="189" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="190" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="191" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="192" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="193" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="194" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="195" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="196" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="197" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="198" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="199" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="200" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="201" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="202" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="203" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="204" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="205" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="206" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="207" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="208" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="209" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="210" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="211" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="212" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="213" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="214" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="215" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="216" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="217" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="218" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="219" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="220" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="221" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="222" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="223" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="224" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="225" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="226" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="227" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="228" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="229" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="230" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="231" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="232" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="233" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="234" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="235" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="236" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="237" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="238" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="239" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="240" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="241" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="242" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="243" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="244" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="245" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="246" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="247" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="248" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="249" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="250" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="251" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="252" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="253" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="254" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="255" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="256" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="257" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="258" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="259" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="260" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="261" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="262" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="263" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="264" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="265" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="266" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="267" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="268" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="269" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="270" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="271" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="272" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="273" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="274" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="275" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="276" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="277" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="278" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="279" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="280" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="281" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="282" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="283" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="284" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="285" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="286" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="287" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="288" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="289" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="290" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="291" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="292" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="293" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="294" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="295" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="296" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="297" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="298" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="299" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="300" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="301" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="302" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="303" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="304" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="305" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="306" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="307" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="308" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="309" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="310" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="311" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="312" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="313" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="314" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="315" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="316" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="317" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="318" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="319" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="320" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="321" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="322" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="323" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="324" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="325" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="326" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="327" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="328" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="329" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="330" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="331" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="332" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="333" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="334" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="335" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="336" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="337" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="338" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="339" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="340" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="341" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="342" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="343" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="344" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="345" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="346" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="347" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="348" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="349" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="350" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="351" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="352" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="353" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="354" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="355" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="356" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="357" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="358" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="359" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="360" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="361" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="362" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="363" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="364" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="365" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="366" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="367" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="368" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="369" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="370" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="371" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="372" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="373" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="374" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="375" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="376" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="377" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="378" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="379" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="380" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="381" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="382" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="383" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="384" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="385" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="386" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="387" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="388" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="389" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="390" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="391" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="392" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="393" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="394" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="395" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="396" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="397" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="398" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="399" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="400" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="401" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="402" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="403" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="404" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="405" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="406" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="407" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="408" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="409" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="410" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="411" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="412" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="413" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="414" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="415" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="416" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="417" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="418" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="419" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="420" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="421" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="422" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="423" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="424" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="425" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="426" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="427" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="428" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="429" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="430" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="431" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="432" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="433" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="434" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="435" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="436" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="437" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="438" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="439" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="440" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="441" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="442" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="443" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="444" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="445" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="446" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="447" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="448" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="449" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="450" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="451" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="452" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="453" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="454" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="455" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="456" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="457" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="458" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="459" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="460" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="461" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="462" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="463" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="464" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="465" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="466" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="467" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="468" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="469" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="470" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="471" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="472" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="473" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="474" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="475" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="476" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="477" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="478" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="479" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="480" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="481" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="482" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="483" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="484" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="485" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="486" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="487" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="488" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="489" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="490" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="491" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="492" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="493" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="494" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="495" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="496" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="497" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="498" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="499" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="500" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="501" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="502" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="503" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="504" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="505" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="506" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="507" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="508" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="509" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="510" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="511" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="512" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="513" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="514" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="515" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="516" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="517" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="518" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="519" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="520" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="521" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="522" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="523" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="524" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="525" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="526" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="527" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="528" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="529" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="530" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="531" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="532" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="533" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="534" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="535" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="536" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="537" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="538" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="539" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="540" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="541" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="542" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="543" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="544" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="545" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="546" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="547" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="548" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="549" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="550" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="551" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="552" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="553" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="554" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="555" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="556" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="557" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="558" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="559" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="560" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="561" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="562" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="563" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="564" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="565" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="566" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="567" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="568" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="569" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="570" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="571" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="572" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="573" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="574" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="575" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="576" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="577" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="578" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="579" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="580" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="581" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="582" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="583" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="584" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="585" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="586" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="587" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="588" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="589" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="590" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="591" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="592" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="593" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="594" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="595" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="596" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="597" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="598" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="599" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="600" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="601" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="602" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="603" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="604" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="605" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="606" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="607" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="608" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="609" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="610" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="611" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="612" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="613" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="614" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="615" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="616" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="617" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="618" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="619" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="620" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="621" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="622" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="623" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="624" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="625" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="626" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="627" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="628" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="629" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="630" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="631" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="632" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="633" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="634" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="635" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="636" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="637" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="638" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="639" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="640" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="641" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="642" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="643" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="644" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="645" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="646" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="647" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="648" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="649" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="650" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="651" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="652" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="653" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="654" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="655" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="656" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="657" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="658" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="659" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="660" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="661" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="662" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="663" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="664" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="665" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="666" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="667" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="668" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="669" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="670" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="671" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="672" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="673" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="674" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="675" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="676" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="677" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="678" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="679" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="680" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="681" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="682" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="683" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="684" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="685" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="686" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="687" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="688" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="689" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="690" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="691" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="692" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="693" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="694" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="695" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="696" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="697" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="698" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="699" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="700" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="701" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="702" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="703" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="704" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="705" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="706" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="707" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="708" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="709" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="710" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="711" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="712" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="713" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="714" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="715" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="716" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="717" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="718" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="719" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="720" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="721" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="722" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="723" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="724" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="725" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="726" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="727" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="728" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="729" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="730" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="731" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="732" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="733" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="734" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="735" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="736" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="737" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="738" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="739" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="740" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="741" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="742" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="743" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="744" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="745" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="746" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="747" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="748" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="749" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="750" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="751" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="752" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="753" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="754" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="755" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="756" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="757" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="758" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="759" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="760" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="761" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="762" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="763" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="764" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="765" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="766" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="767" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="768" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="769" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="770" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="771" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="772" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="773" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="774" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="775" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="776" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="777" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="778" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="779" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="780" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="781" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="782" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="783" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="784" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="785" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="786" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="787" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="788" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="789" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="790" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="791" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="792" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="793" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="794" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="795" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="796" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="797" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="798" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="799" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="800" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="801" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="802" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="803" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="804" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="805" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="806" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="807" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="808" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="809" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="810" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="811" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="812" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="813" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="814" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="815" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="816" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="817" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="818" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="819" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="820" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="821" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="822" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="823" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="824" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="825" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="826" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="827" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="828" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="829" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="830" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="831" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="832" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="833" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="834" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="835" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="836" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="837" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="838" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="839" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="840" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="841" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="842" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="843" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="844" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="845" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="846" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="847" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="848" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="849" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="850" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="851" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="852" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="853" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="854" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="855" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="856" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="857" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="858" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="859" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="860" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="861" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="862" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="863" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="864" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="865" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="866" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="867" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="868" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="869" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="870" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="871" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="872" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="873" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="874" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="875" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="876" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="877" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="878" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="879" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="880" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="881" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="882" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="883" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="884" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="885" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="886" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="887" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="888" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="889" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="890" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="891" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="892" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="893" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="894" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="895" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="896" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="897" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="898" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="899" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="900" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="901" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="902" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="903" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="904" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="905" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="906" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="907" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="908" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="909" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="910" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="911" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="912" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="913" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="914" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="915" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="916" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="917" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="918" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="919" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="920" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="921" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="922" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="923" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="924" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="925" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="926" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="927" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="928" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="929" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="930" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="931" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="932" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="933" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="934" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="935" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="936" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="937" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="938" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="939" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="940" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="941" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="942" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="943" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="944" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="945" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="946" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="947" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="948" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="949" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="950" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="951" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="952" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="953" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="954" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="955" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="956" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="957" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="958" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="959" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="960" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="961" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="962" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="963" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="964" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="965" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="966" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="967" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="968" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="969" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="970" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="971" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="972" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="973" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="974" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="975" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="976" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="977" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="978" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="979" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="980" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="981" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="982" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="983" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="984" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="985" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="986" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="987" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="988" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="989" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="990" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="991" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="992" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="993" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="994" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="995" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="996" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="997" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="998" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="999" spans="1:26" customHeight="1" ht="15.75"/>
+    <row r="1000" spans="1:26" customHeight="1" ht="15.75"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <printOptions gridLines="false" gridLinesSet="true"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>